--- a/New_Outputs/mediation/Stats_Mediation_ROE_receptor_NRS.xlsx
+++ b/New_Outputs/mediation/Stats_Mediation_ROE_receptor_NRS.xlsx
@@ -2352,7 +2352,7 @@
         <v>40</v>
       </c>
       <c r="B2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
         <v>76</v>
@@ -2360,13 +2360,19 @@
       <c r="D2" t="s">
         <v>41</v>
       </c>
+      <c r="E2">
+        <v>0.1072622495056885</v>
+      </c>
+      <c r="F2">
+        <v>0.6620614078209495</v>
+      </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>40</v>
       </c>
       <c r="B3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
         <v>76</v>
@@ -2374,13 +2380,19 @@
       <c r="D3" t="s">
         <v>42</v>
       </c>
+      <c r="E3">
+        <v>-0.08894236834942722</v>
+      </c>
+      <c r="F3">
+        <v>0.7172849676290375</v>
+      </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>40</v>
       </c>
       <c r="B4">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
         <v>76</v>
@@ -2388,13 +2400,19 @@
       <c r="D4" t="s">
         <v>43</v>
       </c>
+      <c r="E4">
+        <v>0.1282776791981364</v>
+      </c>
+      <c r="F4">
+        <v>0.6007237043231346</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>40</v>
       </c>
       <c r="B5">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
         <v>76</v>
@@ -2402,13 +2420,19 @@
       <c r="D5" t="s">
         <v>39</v>
       </c>
+      <c r="E5">
+        <v>0.4692488926217691</v>
+      </c>
+      <c r="F5">
+        <v>0.04267631785737819</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>40</v>
       </c>
       <c r="B6">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
         <v>41</v>
@@ -2417,10 +2441,10 @@
         <v>42</v>
       </c>
       <c r="E6">
-        <v>0.352094560340815</v>
+        <v>0.3001569039626704</v>
       </c>
       <c r="F6">
-        <v>0.09941989674100854</v>
+        <v>0.2118236880738064</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2428,7 +2452,7 @@
         <v>40</v>
       </c>
       <c r="B7">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
         <v>41</v>
@@ -2437,10 +2461,10 @@
         <v>43</v>
       </c>
       <c r="E7">
-        <v>-0.1750438044988212</v>
+        <v>-0.3960031878955979</v>
       </c>
       <c r="F7">
-        <v>0.4243703065188297</v>
+        <v>0.09327321998935369</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2448,7 +2472,7 @@
         <v>40</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
         <v>41</v>
@@ -2457,10 +2481,10 @@
         <v>39</v>
       </c>
       <c r="E8">
-        <v>0.5235969652488727</v>
+        <v>0.6146492576426417</v>
       </c>
       <c r="F8">
-        <v>0.01034345000958748</v>
+        <v>0.005104894754993412</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2468,7 +2492,7 @@
         <v>40</v>
       </c>
       <c r="B9">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
@@ -2477,10 +2501,10 @@
         <v>43</v>
       </c>
       <c r="E9">
-        <v>0.3608144848386189</v>
+        <v>0.2908185102333419</v>
       </c>
       <c r="F9">
-        <v>0.0907544506536464</v>
+        <v>0.2270808601327775</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2488,7 +2512,7 @@
         <v>40</v>
       </c>
       <c r="B10">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
         <v>42</v>
@@ -2497,10 +2521,10 @@
         <v>39</v>
       </c>
       <c r="E10">
-        <v>0.0638325827686323</v>
+        <v>0.2132585868283918</v>
       </c>
       <c r="F10">
-        <v>0.7723108512202524</v>
+        <v>0.3806973339016984</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2508,7 +2532,7 @@
         <v>40</v>
       </c>
       <c r="B11">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
         <v>43</v>
@@ -2517,10 +2541,10 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>-0.2192945203261976</v>
+        <v>-0.1997693415341527</v>
       </c>
       <c r="F11">
-        <v>0.3147253374843179</v>
+        <v>0.4122317470397217</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2528,7 +2552,7 @@
         <v>44</v>
       </c>
       <c r="B12">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
         <v>76</v>
@@ -2536,13 +2560,19 @@
       <c r="D12" t="s">
         <v>41</v>
       </c>
+      <c r="E12">
+        <v>0.1318121803859448</v>
+      </c>
+      <c r="F12">
+        <v>0.6140584002308742</v>
+      </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>44</v>
       </c>
       <c r="B13">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
         <v>76</v>
@@ -2550,13 +2580,19 @@
       <c r="D13" t="s">
         <v>42</v>
       </c>
+      <c r="E13">
+        <v>0.2212517115230526</v>
+      </c>
+      <c r="F13">
+        <v>0.3934325284293826</v>
+      </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>44</v>
       </c>
       <c r="B14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
         <v>76</v>
@@ -2564,13 +2600,19 @@
       <c r="D14" t="s">
         <v>43</v>
       </c>
+      <c r="E14">
+        <v>0.3522932556069947</v>
+      </c>
+      <c r="F14">
+        <v>0.1654887019496943</v>
+      </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>44</v>
       </c>
       <c r="B15">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
         <v>76</v>
@@ -2578,13 +2620,19 @@
       <c r="D15" t="s">
         <v>39</v>
       </c>
+      <c r="E15">
+        <v>-0.4593926392259144</v>
+      </c>
+      <c r="F15">
+        <v>0.06357888832011317</v>
+      </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>44</v>
       </c>
       <c r="B16">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
         <v>41</v>
@@ -2593,10 +2641,10 @@
         <v>42</v>
       </c>
       <c r="E16">
-        <v>0.5304056152604507</v>
+        <v>0.4431162573249574</v>
       </c>
       <c r="F16">
-        <v>0.01337898153608782</v>
+        <v>0.07484300678264408</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2604,7 +2652,7 @@
         <v>44</v>
       </c>
       <c r="B17">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
         <v>41</v>
@@ -2613,10 +2661,10 @@
         <v>43</v>
       </c>
       <c r="E17">
-        <v>0.2753503576009841</v>
+        <v>0.2903619289978745</v>
       </c>
       <c r="F17">
-        <v>0.2270188237927374</v>
+        <v>0.2582334626769702</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2624,7 +2672,7 @@
         <v>44</v>
       </c>
       <c r="B18">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
         <v>41</v>
@@ -2633,10 +2681,10 @@
         <v>39</v>
       </c>
       <c r="E18">
-        <v>0.1204973937828491</v>
+        <v>0.05940870964706638</v>
       </c>
       <c r="F18">
-        <v>0.6028694676852762</v>
+        <v>0.820820427819039</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2644,7 +2692,7 @@
         <v>44</v>
       </c>
       <c r="B19">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C19" t="s">
         <v>42</v>
@@ -2653,10 +2701,10 @@
         <v>43</v>
       </c>
       <c r="E19">
-        <v>0.2768046884218075</v>
+        <v>0.3435397918642999</v>
       </c>
       <c r="F19">
-        <v>0.2244743030965972</v>
+        <v>0.1769893822256257</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2664,7 +2712,7 @@
         <v>44</v>
       </c>
       <c r="B20">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
         <v>42</v>
@@ -2673,10 +2721,10 @@
         <v>39</v>
       </c>
       <c r="E20">
-        <v>0.4631371369841585</v>
+        <v>0.4918182701330511</v>
       </c>
       <c r="F20">
-        <v>0.03448487100901386</v>
+        <v>0.04493943782859358</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2684,7 +2732,7 @@
         <v>44</v>
       </c>
       <c r="B21">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C21" t="s">
         <v>43</v>
@@ -2693,10 +2741,10 @@
         <v>39</v>
       </c>
       <c r="E21">
-        <v>-0.08963114781871953</v>
+        <v>-0.1959784825160999</v>
       </c>
       <c r="F21">
-        <v>0.6992228534429602</v>
+        <v>0.4509404396379546</v>
       </c>
     </row>
   </sheetData>

--- a/New_Outputs/mediation/Stats_Mediation_ROE_receptor_NRS.xlsx
+++ b/New_Outputs/mediation/Stats_Mediation_ROE_receptor_NRS.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="77">
   <si>
     <t>outcome</t>
   </si>
@@ -724,109 +724,109 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>0.1072622495056885</v>
+        <v>0.1167132846248926</v>
       </c>
       <c r="F2">
-        <v>0.2411363795022837</v>
+        <v>0.2167265128914745</v>
       </c>
       <c r="G2">
-        <v>0.6620614078209496</v>
+        <v>0.5958755166414317</v>
       </c>
       <c r="H2">
-        <v>-0.6031343808665101</v>
+        <v>-0.3600472985304451</v>
       </c>
       <c r="I2">
-        <v>0.6532874284057618</v>
+        <v>0.4912682898001515</v>
       </c>
       <c r="J2">
-        <v>0.570884702913583</v>
+        <v>0.5116398734165162</v>
       </c>
       <c r="K2">
-        <v>0.1701051819568235</v>
+        <v>0.1904435029613049</v>
       </c>
       <c r="L2">
-        <v>0.004015571334531583</v>
+        <v>0.01418859194096277</v>
       </c>
       <c r="M2">
-        <v>0.2542409906144491</v>
+        <v>0.1378960295475792</v>
       </c>
       <c r="N2">
-        <v>0.88115259070306</v>
+        <v>0.7685510139342548</v>
       </c>
       <c r="O2">
-        <v>0.4080145151788716</v>
+        <v>0.1024484219665804</v>
       </c>
       <c r="P2">
-        <v>0.1701051819568235</v>
+        <v>0.1904435029613049</v>
       </c>
       <c r="Q2">
-        <v>0.02899989459508437</v>
+        <v>0.5965501416413892</v>
       </c>
       <c r="R2">
-        <v>0.1095996532272835</v>
+        <v>-0.3260292133673632</v>
       </c>
       <c r="S2">
-        <v>0.7304654285429516</v>
+        <v>0.5111890839013912</v>
       </c>
       <c r="T2">
-        <v>0.4692488926217689</v>
+        <v>0.1621635921380862</v>
       </c>
       <c r="U2">
-        <v>0.2141749527802587</v>
+        <v>0.215329533659334</v>
       </c>
       <c r="V2">
-        <v>0.04267631785737821</v>
+        <v>0.4597529907634764</v>
       </c>
       <c r="W2">
-        <v>-0.0129290690188673</v>
+        <v>-0.2546691874886765</v>
       </c>
       <c r="X2">
-        <v>0.7725641128859382</v>
+        <v>0.5601671162851848</v>
       </c>
       <c r="Y2">
-        <v>0.0612343774428976</v>
+        <v>0.05971517017150589</v>
       </c>
       <c r="Z2">
-        <v>0.1388649771061662</v>
+        <v>0.1130917361171206</v>
       </c>
       <c r="AA2">
-        <v>-0.4772586397993623</v>
+        <v>-0.2008583182998206</v>
       </c>
       <c r="AB2">
-        <v>0.3537255176558926</v>
+        <v>0.2873382674381784</v>
       </c>
       <c r="AC2">
-        <v>0.7784</v>
+        <v>0.5988</v>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>0.1304944527429171</v>
+        <v>0.3682403021798937</v>
       </c>
       <c r="AF2">
-        <v>0.07981220085846845</v>
+        <v>0.03397408640497605</v>
       </c>
       <c r="AG2">
-        <v>2.587138614835161</v>
+        <v>2.397938528513134</v>
       </c>
       <c r="AH2">
-        <v>1.375844308585351</v>
+        <v>0.1397675755035535</v>
       </c>
       <c r="AI2">
-        <v>1.582329535361275</v>
+        <v>0.2212353462650801</v>
       </c>
       <c r="AJ2">
-        <v>0.2064852267759237</v>
+        <v>0.08146777076152634</v>
       </c>
       <c r="AK2">
-        <v>0.01150519016902058</v>
+        <v>0.01362199080793121</v>
       </c>
       <c r="AL2">
-        <v>0.5423542182666672</v>
+        <v>0.2845064891361843</v>
       </c>
       <c r="AM2">
         <v>5000</v>
@@ -843,109 +843,109 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>-0.08894236834942712</v>
+        <v>-0.03499378396413864</v>
       </c>
       <c r="F3">
-        <v>0.2415744015354269</v>
+        <v>0.2180842383208696</v>
       </c>
       <c r="G3">
-        <v>0.7172849676290377</v>
+        <v>0.8740522877794723</v>
       </c>
       <c r="H3">
-        <v>-0.4071997884420405</v>
+        <v>-0.423985559113412</v>
       </c>
       <c r="I3">
-        <v>0.3213257483760705</v>
+        <v>0.3800732381319121</v>
       </c>
       <c r="J3">
-        <v>0.2570279774420391</v>
+        <v>0.06959252103844964</v>
       </c>
       <c r="K3">
-        <v>0.2121261604320802</v>
+        <v>0.2202332484901988</v>
       </c>
       <c r="L3">
-        <v>0.2432283212671865</v>
+        <v>0.7552806267536645</v>
       </c>
       <c r="M3">
-        <v>-0.2648069564315745</v>
+        <v>-0.339763587633921</v>
       </c>
       <c r="N3">
-        <v>0.6371684768795536</v>
+        <v>0.5134598607650988</v>
       </c>
       <c r="O3">
-        <v>0.492109569667527</v>
+        <v>0.1645988977848254</v>
       </c>
       <c r="P3">
-        <v>0.2121261604320802</v>
+        <v>0.2202332484901988</v>
       </c>
       <c r="Q3">
-        <v>0.0338921169339256</v>
+        <v>0.4635288488096574</v>
       </c>
       <c r="R3">
-        <v>0.0694322628964226</v>
+        <v>-0.2722338758586049</v>
       </c>
       <c r="S3">
-        <v>0.778117350909452</v>
+        <v>0.6135710519703101</v>
       </c>
       <c r="T3">
-        <v>0.4692488926217689</v>
+        <v>0.1621635921380862</v>
       </c>
       <c r="U3">
-        <v>0.2141749527802587</v>
+        <v>0.215329533659334</v>
       </c>
       <c r="V3">
-        <v>0.04267631785737821</v>
+        <v>0.4597529907634764</v>
       </c>
       <c r="W3">
-        <v>-0.007668788949198267</v>
+        <v>-0.2706694947259489</v>
       </c>
       <c r="X3">
-        <v>0.7665585062796862</v>
+        <v>0.5487715690108982</v>
       </c>
       <c r="Y3">
-        <v>-0.02286067704575809</v>
+        <v>-0.00243530564673928</v>
       </c>
       <c r="Z3">
-        <v>0.06489455489396594</v>
+        <v>0.01702166218266489</v>
       </c>
       <c r="AA3">
-        <v>-0.2029868841339345</v>
+        <v>-0.1509187456260273</v>
       </c>
       <c r="AB3">
-        <v>0.05979390666661977</v>
+        <v>0.06754245761941921</v>
       </c>
       <c r="AC3">
-        <v>0.606</v>
+        <v>0.7272</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>-0.04871759402144098</v>
+        <v>-0.01501758572704506</v>
       </c>
       <c r="AF3">
-        <v>-0.04350803789487916</v>
+        <v>-0.007139304383540265</v>
       </c>
       <c r="AG3">
-        <v>1.771794170495994</v>
+        <v>0.4653703778267543</v>
       </c>
       <c r="AH3">
-        <v>1.65941682327314</v>
+        <v>0.2245577670434681</v>
       </c>
       <c r="AI3">
-        <v>1.582329535361275</v>
+        <v>0.2212353462650801</v>
       </c>
       <c r="AJ3">
-        <v>-0.07708728791186568</v>
+        <v>-0.003322420778388336</v>
       </c>
       <c r="AK3">
-        <v>0.007910744887605179</v>
+        <v>0.001224564916128802</v>
       </c>
       <c r="AL3">
-        <v>0.2857352938597115</v>
+        <v>0.0311342188860216</v>
       </c>
       <c r="AM3">
         <v>5000</v>
@@ -962,109 +962,109 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>0.1282776791981364</v>
+        <v>0.3978053951395698</v>
       </c>
       <c r="F4">
-        <v>0.2405318661803633</v>
+        <v>0.2002083281172806</v>
       </c>
       <c r="G4">
-        <v>0.6007237043231346</v>
+        <v>0.060128277905319</v>
       </c>
       <c r="H4">
-        <v>-0.316790710629502</v>
+        <v>0.01044536269929236</v>
       </c>
       <c r="I4">
-        <v>0.554727641232</v>
+        <v>0.6852834553242261</v>
       </c>
       <c r="J4">
-        <v>-0.264312810825933</v>
+        <v>-0.3371592273897474</v>
       </c>
       <c r="K4">
-        <v>0.2125721529631003</v>
+        <v>0.2283728034919489</v>
       </c>
       <c r="L4">
-        <v>0.2316309263080705</v>
+        <v>0.1554211973383918</v>
       </c>
       <c r="M4">
-        <v>-0.5982602551811175</v>
+        <v>-0.6860051191955492</v>
       </c>
       <c r="N4">
-        <v>0.1578218994382697</v>
+        <v>0.1406114454524924</v>
       </c>
       <c r="O4">
-        <v>0.5031543265768555</v>
+        <v>0.2962873518148166</v>
       </c>
       <c r="P4">
-        <v>0.2125721529631003</v>
+        <v>0.2283728034919489</v>
       </c>
       <c r="Q4">
-        <v>0.03087957842271286</v>
+        <v>0.2092652619415088</v>
       </c>
       <c r="R4">
-        <v>0.003136738806601418</v>
+        <v>-0.15393985696042</v>
       </c>
       <c r="S4">
-        <v>0.808982911782143</v>
+        <v>0.6648488870446585</v>
       </c>
       <c r="T4">
-        <v>0.4692488926217689</v>
+        <v>0.1621635921380862</v>
       </c>
       <c r="U4">
-        <v>0.2141749527802587</v>
+        <v>0.215329533659334</v>
       </c>
       <c r="V4">
-        <v>0.04267631785737821</v>
+        <v>0.4597529907634764</v>
       </c>
       <c r="W4">
-        <v>-0.008463258527633024</v>
+        <v>-0.2586529568592761</v>
       </c>
       <c r="X4">
-        <v>0.7643042981150363</v>
+        <v>0.5607616974171555</v>
       </c>
       <c r="Y4">
-        <v>-0.03390543395508674</v>
+        <v>-0.1341237596767305</v>
       </c>
       <c r="Z4">
-        <v>0.06917674372870351</v>
+        <v>0.1131807337865657</v>
       </c>
       <c r="AA4">
-        <v>-0.2193085720585018</v>
+        <v>-0.3873109668155618</v>
       </c>
       <c r="AB4">
-        <v>0.1135431585672093</v>
+        <v>0.0625732459436262</v>
       </c>
       <c r="AC4">
-        <v>0.6820000000000001</v>
+        <v>0.1808</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>-0.07225469146160717</v>
+        <v>-0.827089224580823</v>
       </c>
       <c r="AF4">
-        <v>0.08529730804943694</v>
+        <v>0.1188768894974412</v>
       </c>
       <c r="AG4">
-        <v>-1.340379139536891</v>
+        <v>-1.539250999633477</v>
       </c>
       <c r="AH4">
-        <v>1.696660267729392</v>
+        <v>0.4042167172573345</v>
       </c>
       <c r="AI4">
-        <v>1.582329535361275</v>
+        <v>0.2212353462650801</v>
       </c>
       <c r="AJ4">
-        <v>-0.1143307323681174</v>
+        <v>-0.1829813709922547</v>
       </c>
       <c r="AK4">
-        <v>0.01645516298046002</v>
+        <v>0.1582491324021494</v>
       </c>
       <c r="AL4">
-        <v>0.2889062067417792</v>
+        <v>0.1219841923193577</v>
       </c>
       <c r="AM4">
         <v>5000</v>
@@ -1081,109 +1081,109 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E5">
-        <v>0.1318121803859447</v>
+        <v>0.186143151641138</v>
       </c>
       <c r="F5">
-        <v>0.2559460293501872</v>
+        <v>0.2254061512140047</v>
       </c>
       <c r="G5">
-        <v>0.6140584002308743</v>
+        <v>0.4191597542572641</v>
       </c>
       <c r="H5">
-        <v>-0.3244078619527487</v>
+        <v>-0.1923797829273587</v>
       </c>
       <c r="I5">
-        <v>0.4332634012373798</v>
+        <v>0.5286440719056948</v>
       </c>
       <c r="J5">
-        <v>0.1220833868876406</v>
+        <v>0.09172316855879828</v>
       </c>
       <c r="K5">
-        <v>0.2372467287043575</v>
+        <v>0.2353433457195432</v>
       </c>
       <c r="L5">
-        <v>0.6148709436016764</v>
+        <v>0.7013004356267193</v>
       </c>
       <c r="M5">
-        <v>-0.2510812865106402</v>
+        <v>-0.2297054415140012</v>
       </c>
       <c r="N5">
-        <v>0.4750308236301193</v>
+        <v>0.4512095867798437</v>
       </c>
       <c r="O5">
-        <v>-0.4754847166404753</v>
+        <v>0.1545811649279694</v>
       </c>
       <c r="P5">
-        <v>0.2372467287043575</v>
+        <v>0.2353433457195432</v>
       </c>
       <c r="Q5">
-        <v>0.06479240799018395</v>
+        <v>0.5195989636249765</v>
       </c>
       <c r="R5">
-        <v>-0.8421200699798445</v>
+        <v>-0.2412886618378324</v>
       </c>
       <c r="S5">
-        <v>0.01809485908767724</v>
+        <v>0.5897129702208586</v>
       </c>
       <c r="T5">
-        <v>-0.4593926392259146</v>
+        <v>0.1716548046020156</v>
       </c>
       <c r="U5">
-        <v>0.2293408530295825</v>
+        <v>0.2260105526247373</v>
       </c>
       <c r="V5">
-        <v>0.06357888832011308</v>
+        <v>0.4568746028438273</v>
       </c>
       <c r="W5">
-        <v>-0.8292553594506227</v>
+        <v>-0.2152211950996728</v>
       </c>
       <c r="X5">
-        <v>-0.001876853438874402</v>
+        <v>0.5876603120203083</v>
       </c>
       <c r="Y5">
-        <v>0.01609207741456076</v>
+        <v>0.01707363967404605</v>
       </c>
       <c r="Z5">
-        <v>0.0442074475072358</v>
+        <v>0.04844126191422003</v>
       </c>
       <c r="AA5">
-        <v>-0.08293441936943546</v>
+        <v>-0.07133293327862808</v>
       </c>
       <c r="AB5">
-        <v>0.1262726950275186</v>
+        <v>0.164607151350368</v>
       </c>
       <c r="AC5">
-        <v>0.712</v>
+        <v>0.6652</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5">
-        <v>-0.03502902754749448</v>
+        <v>0.0994649681588089</v>
       </c>
       <c r="AF5">
-        <v>0.1746034567330501</v>
+        <v>0.07444824432236181</v>
       </c>
       <c r="AG5">
-        <v>0.6805961087246315</v>
+        <v>0.5096642556860477</v>
       </c>
       <c r="AH5">
-        <v>-3.511290391677424</v>
+        <v>0.3435335052957036</v>
       </c>
       <c r="AI5">
-        <v>-3.392455958455038</v>
+        <v>0.3814771143253933</v>
       </c>
       <c r="AJ5">
-        <v>0.1188344332223834</v>
+        <v>0.03794360902968956</v>
       </c>
       <c r="AK5">
-        <v>0.01737445089809684</v>
+        <v>0.03464927290289568</v>
       </c>
       <c r="AL5">
-        <v>0.2256869953733924</v>
+        <v>0.03758700242170269</v>
       </c>
       <c r="AM5">
         <v>5000</v>
@@ -1200,109 +1200,109 @@
         <v>42</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>0.2212517115230526</v>
+        <v>0.1710408821198427</v>
       </c>
       <c r="F6">
-        <v>0.2517998782297985</v>
+        <v>0.2260350481258284</v>
       </c>
       <c r="G6">
-        <v>0.3934325284293826</v>
+        <v>0.4585103373475866</v>
       </c>
       <c r="H6">
-        <v>-0.3073953275898358</v>
+        <v>-0.3564533585711889</v>
       </c>
       <c r="I6">
-        <v>0.6485177105499946</v>
+        <v>0.6351263276258035</v>
       </c>
       <c r="J6">
-        <v>0.6240062304031371</v>
+        <v>0.4468497291747092</v>
       </c>
       <c r="K6">
-        <v>0.1773180937314105</v>
+        <v>0.2108328182532421</v>
       </c>
       <c r="L6">
-        <v>0.003403316967875259</v>
+        <v>0.04821445347274762</v>
       </c>
       <c r="M6">
-        <v>0.1864130040175316</v>
+        <v>0.07320655599083817</v>
       </c>
       <c r="N6">
-        <v>0.9847466458636173</v>
+        <v>0.8001867701519865</v>
       </c>
       <c r="O6">
-        <v>-0.5974550857036566</v>
+        <v>0.09522523274896047</v>
       </c>
       <c r="P6">
-        <v>0.1773180937314104</v>
+        <v>0.2108328182532421</v>
       </c>
       <c r="Q6">
-        <v>0.004583616726171189</v>
+        <v>0.6569071673660192</v>
       </c>
       <c r="R6">
-        <v>-0.891145814813515</v>
+        <v>-0.4398685579600173</v>
       </c>
       <c r="S6">
-        <v>-0.2434392803049127</v>
+        <v>0.5549382304181385</v>
       </c>
       <c r="T6">
-        <v>-0.4593926392259146</v>
+        <v>0.1716548046020156</v>
       </c>
       <c r="U6">
-        <v>0.2293408530295825</v>
+        <v>0.2260105526247373</v>
       </c>
       <c r="V6">
-        <v>0.06357888832011308</v>
+        <v>0.4568746028438273</v>
       </c>
       <c r="W6">
-        <v>-0.8302970133543845</v>
+        <v>-0.2451228597102795</v>
       </c>
       <c r="X6">
-        <v>-0.00790230037766159</v>
+        <v>0.5944592182240349</v>
       </c>
       <c r="Y6">
-        <v>0.1380624464777424</v>
+        <v>0.07642957185305506</v>
       </c>
       <c r="Z6">
-        <v>0.1619484904641395</v>
+        <v>0.1072480554312204</v>
       </c>
       <c r="AA6">
-        <v>-0.1424116311314551</v>
+        <v>-0.1628276941253636</v>
       </c>
       <c r="AB6">
-        <v>0.5929115884042764</v>
+        <v>0.4411098263768993</v>
       </c>
       <c r="AC6">
-        <v>0.4464</v>
+        <v>0.55</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6">
-        <v>-0.3005325612321092</v>
+        <v>0.4452515735301335</v>
       </c>
       <c r="AF6">
-        <v>0.1871239622316052</v>
+        <v>0.04965282860893042</v>
       </c>
       <c r="AG6">
-        <v>5.448492357166542</v>
+        <v>3.420817910634936</v>
       </c>
       <c r="AH6">
-        <v>-4.411999436516663</v>
+        <v>0.2116238289062773</v>
       </c>
       <c r="AI6">
-        <v>-3.392455958455038</v>
+        <v>0.3814771143253933</v>
       </c>
       <c r="AJ6">
-        <v>1.019543478061622</v>
+        <v>0.169853285419116</v>
       </c>
       <c r="AK6">
-        <v>0.04895231985188005</v>
+        <v>0.02925498335633395</v>
       </c>
       <c r="AL6">
-        <v>0.581364133429465</v>
+        <v>0.2232985729528257</v>
       </c>
       <c r="AM6">
         <v>5000</v>
@@ -1319,109 +1319,109 @@
         <v>43</v>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E7">
-        <v>0.3522932556069948</v>
+        <v>0.3270279759063124</v>
       </c>
       <c r="F7">
-        <v>0.2416456720150153</v>
+        <v>0.2168012311790906</v>
       </c>
       <c r="G7">
-        <v>0.1654887019496943</v>
+        <v>0.1478954452114366</v>
       </c>
       <c r="H7">
-        <v>-0.2782984822286802</v>
+        <v>0.01737986780951687</v>
       </c>
       <c r="I7">
-        <v>0.6556917425091964</v>
+        <v>0.5781994303782836</v>
       </c>
       <c r="J7">
-        <v>-0.03897472857050436</v>
+        <v>-0.1632233692779639</v>
       </c>
       <c r="K7">
-        <v>0.2534380845873048</v>
+        <v>0.2426839376680916</v>
       </c>
       <c r="L7">
-        <v>0.8799747781213378</v>
+        <v>0.5097598228639977</v>
       </c>
       <c r="M7">
-        <v>-0.4913273596286238</v>
+        <v>-0.6139347171292616</v>
       </c>
       <c r="N7">
-        <v>0.3808452494343136</v>
+        <v>0.2875925871570365</v>
       </c>
       <c r="O7">
-        <v>-0.4456621052114125</v>
+        <v>0.2250334126775968</v>
       </c>
       <c r="P7">
-        <v>0.2534380845873047</v>
+        <v>0.2426839376680917</v>
       </c>
       <c r="Q7">
-        <v>0.1004980282522921</v>
+        <v>0.3660540840994794</v>
       </c>
       <c r="R7">
-        <v>-0.8431696234986928</v>
+        <v>-0.1754975863703593</v>
       </c>
       <c r="S7">
-        <v>0.09406161925759111</v>
+        <v>0.6240974632297412</v>
       </c>
       <c r="T7">
-        <v>-0.4593926392259146</v>
+        <v>0.1716548046020156</v>
       </c>
       <c r="U7">
-        <v>0.2293408530295825</v>
+        <v>0.2260105526247373</v>
       </c>
       <c r="V7">
-        <v>0.06357888832011308</v>
+        <v>0.4568746028438273</v>
       </c>
       <c r="W7">
-        <v>-0.8334486689405465</v>
+        <v>-0.2243289336498806</v>
       </c>
       <c r="X7">
-        <v>0.007295180672956251</v>
+        <v>0.5850497801573855</v>
       </c>
       <c r="Y7">
-        <v>-0.01373053401450193</v>
+        <v>-0.05337860807558112</v>
       </c>
       <c r="Z7">
-        <v>0.08977988110758305</v>
+        <v>0.08689623442420662</v>
       </c>
       <c r="AA7">
-        <v>-0.2441075735861157</v>
+        <v>-0.266848391406063</v>
       </c>
       <c r="AB7">
-        <v>0.1411999269828708</v>
+        <v>0.08775546827651541</v>
       </c>
       <c r="AC7">
-        <v>0.8716</v>
+        <v>0.5124</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7">
-        <v>0.02988845018857539</v>
+        <v>-0.3109648354984311</v>
       </c>
       <c r="AF7">
-        <v>0.6091947623685342</v>
+        <v>0.1663386549143173</v>
       </c>
       <c r="AG7">
-        <v>-0.1664414358012501</v>
+        <v>-0.7131593565170847</v>
       </c>
       <c r="AH7">
-        <v>-3.291060707523819</v>
+        <v>0.5001030824280051</v>
       </c>
       <c r="AI7">
-        <v>-3.392455958455038</v>
+        <v>0.3814771143253933</v>
       </c>
       <c r="AJ7">
-        <v>-0.1013952509312202</v>
+        <v>-0.1186259681026119</v>
       </c>
       <c r="AK7">
-        <v>0.1241105379461753</v>
+        <v>0.1069472970253796</v>
       </c>
       <c r="AL7">
-        <v>0.2123720988777725</v>
+        <v>0.05325796442132021</v>
       </c>
       <c r="AM7">
         <v>5000</v>
@@ -1516,58 +1516,58 @@
         <v>55</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>0.04514230002833684</v>
+        <v>0.04264153049745985</v>
       </c>
       <c r="G2">
-        <v>-0.4792315068088483</v>
+        <v>-0.2290057939882075</v>
       </c>
       <c r="H2">
-        <v>0.3493182903291439</v>
+        <v>0.2765194067555672</v>
       </c>
       <c r="I2">
-        <v>0.8336</v>
+        <v>0.772</v>
       </c>
       <c r="J2">
-        <v>-0.0245499308802562</v>
+        <v>-0.06942986701624532</v>
       </c>
       <c r="K2">
-        <v>-0.7763237091305263</v>
+        <v>-0.61792404383372</v>
       </c>
       <c r="L2">
-        <v>0.6762942733908955</v>
+        <v>0.4650056543007606</v>
       </c>
       <c r="M2">
-        <v>0.9704</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="N2">
-        <v>0.4488013160259424</v>
+        <v>0.4199167048577179</v>
       </c>
       <c r="O2">
-        <v>0.01176337496558217</v>
+        <v>-0.06829766823495746</v>
       </c>
       <c r="P2">
-        <v>0.9404110391198366</v>
+        <v>0.842601187586866</v>
       </c>
       <c r="Q2">
-        <v>0.0472</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="R2">
-        <v>0.8834992318193469</v>
+        <v>-0.05213274296138905</v>
       </c>
       <c r="S2">
-        <v>0.3245921091223166</v>
+        <v>-0.6631550564312459</v>
       </c>
       <c r="T2">
-        <v>1.372333339965731</v>
+        <v>0.5402355594704973</v>
       </c>
       <c r="U2">
-        <v>0.0048</v>
+        <v>0.9136</v>
       </c>
       <c r="V2">
         <v>5000</v>
@@ -1584,58 +1584,58 @@
         <v>55</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>-0.1609231235235005</v>
+        <v>-0.07886487749979434</v>
       </c>
       <c r="G3">
-        <v>-0.6557342029706411</v>
+        <v>-0.4732104781494667</v>
       </c>
       <c r="H3">
-        <v>0.1358003301174261</v>
+        <v>0.1649086362666905</v>
       </c>
       <c r="I3">
-        <v>0.35</v>
+        <v>0.4852</v>
       </c>
       <c r="J3">
-        <v>-0.3101940798724798</v>
+        <v>-0.2060346660839813</v>
       </c>
       <c r="K3">
-        <v>-0.8562637801277229</v>
+        <v>-0.8180250598424869</v>
       </c>
       <c r="L3">
-        <v>0.3611019109213614</v>
+        <v>0.4779451068633443</v>
       </c>
       <c r="M3">
-        <v>0.3892</v>
+        <v>0.5464</v>
       </c>
       <c r="N3">
-        <v>-0.3669782529610979</v>
+        <v>-0.3772572081362596</v>
       </c>
       <c r="O3">
-        <v>-1.017060735016327</v>
+        <v>-0.9435990663060412</v>
       </c>
       <c r="P3">
-        <v>0.2134302994572671</v>
+        <v>0.1671714215969972</v>
       </c>
       <c r="Q3">
-        <v>0.2108</v>
+        <v>0.1804</v>
       </c>
       <c r="R3">
-        <v>1.089564655371184</v>
+        <v>0.06937366503586495</v>
       </c>
       <c r="S3">
-        <v>0.5562038511954466</v>
+        <v>-0.5246259855634898</v>
       </c>
       <c r="T3">
-        <v>1.537186285420722</v>
+        <v>0.7456051749468731</v>
       </c>
       <c r="U3">
-        <v>0.0004</v>
+        <v>0.7896</v>
       </c>
       <c r="V3">
         <v>5000</v>
@@ -1652,58 +1652,58 @@
         <v>55</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>-0.02017489994058481</v>
+        <v>-0.08074515160114942</v>
       </c>
       <c r="G4">
-        <v>-0.2500322865120664</v>
+        <v>-0.3804336070196388</v>
       </c>
       <c r="H4">
-        <v>0.2727629645105484</v>
+        <v>0.2217381842101042</v>
       </c>
       <c r="I4">
-        <v>0.8932</v>
+        <v>0.6364</v>
       </c>
       <c r="J4">
-        <v>-0.2240155764088584</v>
+        <v>0.07077741923325737</v>
       </c>
       <c r="K4">
-        <v>-0.755243338961037</v>
+        <v>-0.3929145125836326</v>
       </c>
       <c r="L4">
-        <v>0.5125418194211095</v>
+        <v>0.4848418411211428</v>
       </c>
       <c r="M4">
-        <v>0.5052</v>
+        <v>0.798</v>
       </c>
       <c r="N4">
-        <v>-0.2253380822554286</v>
+        <v>-0.1739358581117835</v>
       </c>
       <c r="O4">
-        <v>-0.7590515039697986</v>
+        <v>-0.7595907055002832</v>
       </c>
       <c r="P4">
-        <v>0.4061640493652345</v>
+        <v>0.4684519881079815</v>
       </c>
       <c r="Q4">
-        <v>0.4596</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="R4">
-        <v>0.948816431788268</v>
+        <v>0.07125393913721981</v>
       </c>
       <c r="S4">
-        <v>0.2110752484005778</v>
+        <v>-0.5212476138754294</v>
       </c>
       <c r="T4">
-        <v>1.467727868613499</v>
+        <v>0.6283766747470794</v>
       </c>
       <c r="U4">
-        <v>0.014</v>
+        <v>0.8064</v>
       </c>
       <c r="V4">
         <v>5000</v>
@@ -1753,22 +1753,22 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
         <v>61</v>
       </c>
       <c r="E2">
-        <v>0.05193535795655221</v>
+        <v>0.05546825865993719</v>
       </c>
       <c r="F2">
-        <v>-0.4111359110006503</v>
+        <v>-0.1908994973627096</v>
       </c>
       <c r="G2">
-        <v>0.3394631643427202</v>
+        <v>0.2731002663852162</v>
       </c>
       <c r="H2">
-        <v>0.8224</v>
+        <v>0.6216</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1779,22 +1779,22 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
         <v>62</v>
       </c>
       <c r="E3">
-        <v>-0.01226085122866857</v>
+        <v>0.0008530386253333064</v>
       </c>
       <c r="F3">
-        <v>-0.1932020995489219</v>
+        <v>-0.1269562038200594</v>
       </c>
       <c r="G3">
-        <v>0.09140246398664295</v>
+        <v>0.1289063033327602</v>
       </c>
       <c r="H3">
-        <v>0.7964</v>
+        <v>0.9883999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1805,22 +1805,22 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
         <v>63</v>
       </c>
       <c r="E4">
-        <v>-0.01346273702567859</v>
+        <v>-0.08006367426559777</v>
       </c>
       <c r="F4">
-        <v>-0.2404135404129563</v>
+        <v>-0.4390444299478201</v>
       </c>
       <c r="G4">
-        <v>0.1163223544853297</v>
+        <v>0.1139726083681702</v>
       </c>
       <c r="H4">
-        <v>0.822</v>
+        <v>0.5052</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1831,22 +1831,22 @@
         <v>40</v>
       </c>
       <c r="C5">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
         <v>64</v>
       </c>
       <c r="E5">
-        <v>0.1072622495056885</v>
+        <v>0.1167132846248926</v>
       </c>
       <c r="F5">
-        <v>-0.6064562079160479</v>
+        <v>-0.3452520977044046</v>
       </c>
       <c r="G5">
-        <v>0.6571075825980077</v>
+        <v>0.4850454392111627</v>
       </c>
       <c r="H5">
-        <v>0.786</v>
+        <v>0.6016</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1857,22 +1857,22 @@
         <v>40</v>
       </c>
       <c r="C6">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
         <v>65</v>
       </c>
       <c r="E6">
-        <v>-0.08894236834942712</v>
+        <v>-0.03499378396413864</v>
       </c>
       <c r="F6">
-        <v>-0.4084359655105334</v>
+        <v>-0.4306433597658834</v>
       </c>
       <c r="G6">
-        <v>0.3121820641914953</v>
+        <v>0.3689580576524832</v>
       </c>
       <c r="H6">
-        <v>0.6568000000000001</v>
+        <v>0.8228</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1883,22 +1883,22 @@
         <v>40</v>
       </c>
       <c r="C7">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
         <v>66</v>
       </c>
       <c r="E7">
-        <v>0.1282776791981364</v>
+        <v>0.3978053951395698</v>
       </c>
       <c r="F7">
-        <v>-0.2897618116636282</v>
+        <v>0.009218455477264071</v>
       </c>
       <c r="G7">
-        <v>0.5476391431350597</v>
+        <v>0.6925688772805249</v>
       </c>
       <c r="H7">
-        <v>0.5452</v>
+        <v>0.0428</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1909,22 +1909,22 @@
         <v>40</v>
       </c>
       <c r="C8">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
         <v>67</v>
       </c>
       <c r="E8">
-        <v>0.4841904602587873</v>
+        <v>0.4752523145776235</v>
       </c>
       <c r="F8">
-        <v>-0.02981775240639307</v>
+        <v>-0.007430739726373915</v>
       </c>
       <c r="G8">
-        <v>0.9529519738194139</v>
+        <v>0.8675159671020479</v>
       </c>
       <c r="H8">
-        <v>0.0612</v>
+        <v>0.0536</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1935,22 +1935,22 @@
         <v>40</v>
       </c>
       <c r="C9">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
         <v>68</v>
       </c>
       <c r="E9">
-        <v>0.1378516387206991</v>
+        <v>-0.02437686150796078</v>
       </c>
       <c r="F9">
-        <v>-0.3589038100480227</v>
+        <v>-0.4825240834720567</v>
       </c>
       <c r="G9">
-        <v>0.788327712793199</v>
+        <v>0.5620457029517285</v>
       </c>
       <c r="H9">
-        <v>0.6204</v>
+        <v>0.9671999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1961,22 +1961,22 @@
         <v>40</v>
       </c>
       <c r="C10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
         <v>69</v>
       </c>
       <c r="E10">
-        <v>-0.1049499578557559</v>
+        <v>-0.2012634198626378</v>
       </c>
       <c r="F10">
-        <v>-0.748657502421146</v>
+        <v>-0.8017148023348319</v>
       </c>
       <c r="G10">
-        <v>0.3593750543110737</v>
+        <v>0.3439516302100015</v>
       </c>
       <c r="H10">
-        <v>0.6375999999999999</v>
+        <v>0.4936</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1987,22 +1987,22 @@
         <v>40</v>
       </c>
       <c r="C11">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
         <v>70</v>
       </c>
       <c r="E11">
-        <v>0.443037122919564</v>
+        <v>0.1859059691184134</v>
       </c>
       <c r="F11">
-        <v>0.1013671330548591</v>
+        <v>-0.1930603135910178</v>
       </c>
       <c r="G11">
-        <v>0.8309418386483625</v>
+        <v>0.6338540412581612</v>
       </c>
       <c r="H11">
-        <v>0.0256</v>
+        <v>0.2792</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2013,22 +2013,22 @@
         <v>40</v>
       </c>
       <c r="C12">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
         <v>71</v>
       </c>
       <c r="E12">
-        <v>0.02621176970220505</v>
+        <v>-0.02374237698032727</v>
       </c>
       <c r="F12">
-        <v>-0.5294121269394906</v>
+        <v>-0.3811392658529121</v>
       </c>
       <c r="G12">
-        <v>0.3440588470080186</v>
+        <v>0.2656049146850222</v>
       </c>
       <c r="H12">
-        <v>0.9728</v>
+        <v>0.7684</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2039,22 +2039,22 @@
         <v>44</v>
       </c>
       <c r="C13">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
         <v>61</v>
       </c>
       <c r="E13">
-        <v>-0.01792913456067112</v>
+        <v>-0.02801643997666221</v>
       </c>
       <c r="F13">
-        <v>-0.1876164364647033</v>
+        <v>-0.2112425156371029</v>
       </c>
       <c r="G13">
-        <v>0.06651437643102524</v>
+        <v>0.08488517287158064</v>
       </c>
       <c r="H13">
-        <v>0.606</v>
+        <v>0.6183999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -2065,22 +2065,22 @@
         <v>44</v>
       </c>
       <c r="C14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
         <v>62</v>
       </c>
       <c r="E14">
-        <v>0.1652200986199768</v>
+        <v>0.1002370347048185</v>
       </c>
       <c r="F14">
-        <v>-0.1887845492249893</v>
+        <v>-0.2226540013359692</v>
       </c>
       <c r="G14">
-        <v>0.6931179265005299</v>
+        <v>0.5526975479684912</v>
       </c>
       <c r="H14">
-        <v>0.4708</v>
+        <v>0.5536</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2091,22 +2091,22 @@
         <v>44</v>
       </c>
       <c r="C15">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
         <v>63</v>
       </c>
       <c r="E15">
-        <v>-0.08015753550416009</v>
+        <v>-0.0889569374638394</v>
       </c>
       <c r="F15">
-        <v>-0.2981527242780335</v>
+        <v>-0.326100118703302</v>
       </c>
       <c r="G15">
-        <v>0.09699236620741111</v>
+        <v>0.05351867449436425</v>
       </c>
       <c r="H15">
-        <v>0.3036</v>
+        <v>0.2344</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -2117,22 +2117,22 @@
         <v>44</v>
       </c>
       <c r="C16">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
         <v>64</v>
       </c>
       <c r="E16">
-        <v>0.1318121803859447</v>
+        <v>0.186143151641138</v>
       </c>
       <c r="F16">
-        <v>-0.3493147426939734</v>
+        <v>-0.191216270597449</v>
       </c>
       <c r="G16">
-        <v>0.4273141369667997</v>
+        <v>0.5085721795197895</v>
       </c>
       <c r="H16">
-        <v>0.4996</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2143,22 +2143,22 @@
         <v>44</v>
       </c>
       <c r="C17">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
         <v>65</v>
       </c>
       <c r="E17">
-        <v>0.2212517115230526</v>
+        <v>0.1710408821198427</v>
       </c>
       <c r="F17">
-        <v>-0.3197810865944787</v>
+        <v>-0.3667011800861592</v>
       </c>
       <c r="G17">
-        <v>0.6484636048751837</v>
+        <v>0.6195206953277399</v>
       </c>
       <c r="H17">
-        <v>0.4732</v>
+        <v>0.5468</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2169,22 +2169,22 @@
         <v>44</v>
       </c>
       <c r="C18">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
         <v>66</v>
       </c>
       <c r="E18">
-        <v>0.3522932556069948</v>
+        <v>0.3270279759063124</v>
       </c>
       <c r="F18">
-        <v>-0.2810756252053638</v>
+        <v>0.01327138451411884</v>
       </c>
       <c r="G18">
-        <v>0.6492639054503799</v>
+        <v>0.5874831700565387</v>
       </c>
       <c r="H18">
-        <v>0.1828</v>
+        <v>0.0432</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2195,22 +2195,22 @@
         <v>44</v>
       </c>
       <c r="C19">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D19" t="s">
         <v>67</v>
       </c>
       <c r="E19">
-        <v>-0.1360203170008628</v>
+        <v>-0.1505101838539545</v>
       </c>
       <c r="F19">
-        <v>-0.5938368051049254</v>
+        <v>-0.6205747121214524</v>
       </c>
       <c r="G19">
-        <v>0.2793313416008381</v>
+        <v>0.3272614061927392</v>
       </c>
       <c r="H19">
-        <v>0.4904</v>
+        <v>0.5096000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -2221,22 +2221,22 @@
         <v>44</v>
       </c>
       <c r="C20">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D20" t="s">
         <v>68</v>
       </c>
       <c r="E20">
-        <v>0.7467517312414653</v>
+        <v>0.5860413806483162</v>
       </c>
       <c r="F20">
-        <v>0.260889160461534</v>
+        <v>0.1965731309033536</v>
       </c>
       <c r="G20">
-        <v>1.221411637116371</v>
+        <v>1.064910694446237</v>
       </c>
       <c r="H20">
-        <v>0.009599999999999999</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -2247,22 +2247,22 @@
         <v>44</v>
       </c>
       <c r="C21">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
         <v>69</v>
       </c>
       <c r="E21">
-        <v>-0.2275307126332866</v>
+        <v>-0.2720162922371019</v>
       </c>
       <c r="F21">
-        <v>-0.5767781326806595</v>
+        <v>-0.7115418887398262</v>
       </c>
       <c r="G21">
-        <v>0.1475891027616108</v>
+        <v>0.2115239723274823</v>
       </c>
       <c r="H21">
-        <v>0.1584</v>
+        <v>0.2296</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -2273,22 +2273,22 @@
         <v>44</v>
       </c>
       <c r="C22">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
         <v>70</v>
       </c>
       <c r="E22">
-        <v>-0.52652606778106</v>
+        <v>0.1883911473376988</v>
       </c>
       <c r="F22">
-        <v>-0.8393550814553405</v>
+        <v>-0.3755297149378861</v>
       </c>
       <c r="G22">
-        <v>-0.1786364547956674</v>
+        <v>0.6536200370563245</v>
       </c>
       <c r="H22">
-        <v>0.0068</v>
+        <v>0.3716</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -2299,22 +2299,22 @@
         <v>44</v>
       </c>
       <c r="C23">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D23" t="s">
         <v>71</v>
       </c>
       <c r="E23">
-        <v>0.06713342855514563</v>
+        <v>-0.01673634273568311</v>
       </c>
       <c r="F23">
-        <v>-0.2558187258967004</v>
+        <v>-0.3922650174530079</v>
       </c>
       <c r="G23">
-        <v>0.5079916329166795</v>
+        <v>0.3937587720934844</v>
       </c>
       <c r="H23">
-        <v>0.8192</v>
+        <v>0.8632</v>
       </c>
     </row>
   </sheetData>
@@ -2352,7 +2352,7 @@
         <v>40</v>
       </c>
       <c r="B2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
         <v>76</v>
@@ -2361,10 +2361,10 @@
         <v>41</v>
       </c>
       <c r="E2">
-        <v>0.1072622495056885</v>
+        <v>0.1167132846248926</v>
       </c>
       <c r="F2">
-        <v>0.6620614078209495</v>
+        <v>0.5958755166414317</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2372,7 +2372,7 @@
         <v>40</v>
       </c>
       <c r="B3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
         <v>76</v>
@@ -2381,10 +2381,10 @@
         <v>42</v>
       </c>
       <c r="E3">
-        <v>-0.08894236834942722</v>
+        <v>-0.03499378396413862</v>
       </c>
       <c r="F3">
-        <v>0.7172849676290375</v>
+        <v>0.8740522877794725</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2392,7 +2392,7 @@
         <v>40</v>
       </c>
       <c r="B4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
         <v>76</v>
@@ -2401,10 +2401,10 @@
         <v>43</v>
       </c>
       <c r="E4">
-        <v>0.1282776791981364</v>
+        <v>0.39780539513957</v>
       </c>
       <c r="F4">
-        <v>0.6007237043231346</v>
+        <v>0.06012827790531899</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2412,7 +2412,7 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
         <v>76</v>
@@ -2421,10 +2421,10 @@
         <v>39</v>
       </c>
       <c r="E5">
-        <v>0.4692488926217691</v>
+        <v>0.1621635921380863</v>
       </c>
       <c r="F5">
-        <v>0.04267631785737819</v>
+        <v>0.4597529907634762</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2432,7 +2432,7 @@
         <v>40</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
         <v>41</v>
@@ -2441,10 +2441,10 @@
         <v>42</v>
       </c>
       <c r="E6">
-        <v>0.3001569039626704</v>
+        <v>0.352094560340815</v>
       </c>
       <c r="F6">
-        <v>0.2118236880738064</v>
+        <v>0.09941989674100854</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2452,7 +2452,7 @@
         <v>40</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
         <v>41</v>
@@ -2461,10 +2461,10 @@
         <v>43</v>
       </c>
       <c r="E7">
-        <v>-0.3960031878955979</v>
+        <v>-0.1750438044988212</v>
       </c>
       <c r="F7">
-        <v>0.09327321998935369</v>
+        <v>0.4243703065188297</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2472,7 +2472,7 @@
         <v>40</v>
       </c>
       <c r="B8">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
         <v>41</v>
@@ -2481,10 +2481,10 @@
         <v>39</v>
       </c>
       <c r="E8">
-        <v>0.6146492576426417</v>
+        <v>0.5235969652488727</v>
       </c>
       <c r="F8">
-        <v>0.005104894754993412</v>
+        <v>0.01034345000958748</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2492,7 +2492,7 @@
         <v>40</v>
       </c>
       <c r="B9">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
@@ -2501,10 +2501,10 @@
         <v>43</v>
       </c>
       <c r="E9">
-        <v>0.2908185102333419</v>
+        <v>0.3608144848386189</v>
       </c>
       <c r="F9">
-        <v>0.2270808601327775</v>
+        <v>0.0907544506536464</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2512,7 +2512,7 @@
         <v>40</v>
       </c>
       <c r="B10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
         <v>42</v>
@@ -2521,10 +2521,10 @@
         <v>39</v>
       </c>
       <c r="E10">
-        <v>0.2132585868283918</v>
+        <v>0.0638325827686323</v>
       </c>
       <c r="F10">
-        <v>0.3806973339016984</v>
+        <v>0.7723108512202524</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2532,7 +2532,7 @@
         <v>40</v>
       </c>
       <c r="B11">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
         <v>43</v>
@@ -2541,10 +2541,10 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>-0.1997693415341527</v>
+        <v>-0.2192945203261976</v>
       </c>
       <c r="F11">
-        <v>0.4122317470397217</v>
+        <v>0.3147253374843179</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2552,7 +2552,7 @@
         <v>44</v>
       </c>
       <c r="B12">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
         <v>76</v>
@@ -2561,10 +2561,10 @@
         <v>41</v>
       </c>
       <c r="E12">
-        <v>0.1318121803859448</v>
+        <v>0.1861431516411379</v>
       </c>
       <c r="F12">
-        <v>0.6140584002308742</v>
+        <v>0.4191597542572641</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2572,7 +2572,7 @@
         <v>44</v>
       </c>
       <c r="B13">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
         <v>76</v>
@@ -2581,10 +2581,10 @@
         <v>42</v>
       </c>
       <c r="E13">
-        <v>0.2212517115230526</v>
+        <v>0.1710408821198426</v>
       </c>
       <c r="F13">
-        <v>0.3934325284293826</v>
+        <v>0.4585103373475866</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2592,7 +2592,7 @@
         <v>44</v>
       </c>
       <c r="B14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
         <v>76</v>
@@ -2601,10 +2601,10 @@
         <v>43</v>
       </c>
       <c r="E14">
-        <v>0.3522932556069947</v>
+        <v>0.3270279759063123</v>
       </c>
       <c r="F14">
-        <v>0.1654887019496943</v>
+        <v>0.1478954452114368</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2612,7 +2612,7 @@
         <v>44</v>
       </c>
       <c r="B15">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
         <v>76</v>
@@ -2621,10 +2621,10 @@
         <v>39</v>
       </c>
       <c r="E15">
-        <v>-0.4593926392259144</v>
+        <v>0.1716548046020155</v>
       </c>
       <c r="F15">
-        <v>0.06357888832011317</v>
+        <v>0.4568746028438276</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2632,7 +2632,7 @@
         <v>44</v>
       </c>
       <c r="B16">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
         <v>41</v>
@@ -2641,10 +2641,10 @@
         <v>42</v>
       </c>
       <c r="E16">
-        <v>0.4431162573249574</v>
+        <v>0.5304056152604507</v>
       </c>
       <c r="F16">
-        <v>0.07484300678264408</v>
+        <v>0.01337898153608782</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2652,7 +2652,7 @@
         <v>44</v>
       </c>
       <c r="B17">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
         <v>41</v>
@@ -2661,10 +2661,10 @@
         <v>43</v>
       </c>
       <c r="E17">
-        <v>0.2903619289978745</v>
+        <v>0.2753503576009841</v>
       </c>
       <c r="F17">
-        <v>0.2582334626769702</v>
+        <v>0.2270188237927374</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2672,7 +2672,7 @@
         <v>44</v>
       </c>
       <c r="B18">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
         <v>41</v>
@@ -2681,10 +2681,10 @@
         <v>39</v>
       </c>
       <c r="E18">
-        <v>0.05940870964706638</v>
+        <v>0.1204973937828491</v>
       </c>
       <c r="F18">
-        <v>0.820820427819039</v>
+        <v>0.6028694676852762</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2692,7 +2692,7 @@
         <v>44</v>
       </c>
       <c r="B19">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
         <v>42</v>
@@ -2701,10 +2701,10 @@
         <v>43</v>
       </c>
       <c r="E19">
-        <v>0.3435397918642999</v>
+        <v>0.2768046884218075</v>
       </c>
       <c r="F19">
-        <v>0.1769893822256257</v>
+        <v>0.2244743030965972</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2712,7 +2712,7 @@
         <v>44</v>
       </c>
       <c r="B20">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
         <v>42</v>
@@ -2721,10 +2721,10 @@
         <v>39</v>
       </c>
       <c r="E20">
-        <v>0.4918182701330511</v>
+        <v>0.4631371369841585</v>
       </c>
       <c r="F20">
-        <v>0.04493943782859358</v>
+        <v>0.03448487100901386</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2732,7 +2732,7 @@
         <v>44</v>
       </c>
       <c r="B21">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C21" t="s">
         <v>43</v>
@@ -2741,10 +2741,10 @@
         <v>39</v>
       </c>
       <c r="E21">
-        <v>-0.1959784825160999</v>
+        <v>-0.08963114781871953</v>
       </c>
       <c r="F21">
-        <v>0.4509404396379546</v>
+        <v>0.6992228534429602</v>
       </c>
     </row>
   </sheetData>
@@ -2754,7 +2754,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1">
@@ -2845,13 +2845,13 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5">
-        <v>-1.715163362357603</v>
+        <v>-6.431798275933005</v>
       </c>
       <c r="B5">
-        <v>1.04024474332027</v>
+        <v>0.00251639309022376</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
         <v>40</v>
@@ -2865,13 +2865,13 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6">
-        <v>-2.739451627363021</v>
+        <v>-1.715163362357603</v>
       </c>
       <c r="B6">
-        <v>0.0278425740267539</v>
+        <v>1.04024474332027</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
         <v>40</v>
@@ -2885,13 +2885,13 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7">
-        <v>-3.397940008672037</v>
+        <v>-2.739451627363021</v>
       </c>
       <c r="B7">
-        <v>0.385368340028758</v>
+        <v>0.0278425740267539</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D7" t="s">
         <v>40</v>
@@ -2905,13 +2905,13 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8">
-        <v>-2.785686102575601</v>
+        <v>-3.397940008672037</v>
       </c>
       <c r="B8">
-        <v>0.27175751463643</v>
+        <v>0.385368340028758</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D8" t="s">
         <v>40</v>
@@ -2925,13 +2925,13 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9">
-        <v>-2.677573947594047</v>
+        <v>-2.785686102575601</v>
       </c>
       <c r="B9">
-        <v>0.11385003334467</v>
+        <v>0.27175751463643</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D9" t="s">
         <v>40</v>
@@ -2945,13 +2945,13 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10">
-        <v>-3.292429823902064</v>
+        <v>-6.431798275933005</v>
       </c>
       <c r="B10">
-        <v>-0.111147107555198</v>
+        <v>-0.664252039254192</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D10" t="s">
         <v>40</v>
@@ -2965,13 +2965,13 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11">
-        <v>-1.654097203523455</v>
+        <v>-6.431798275933005</v>
       </c>
       <c r="B11">
-        <v>-0.848791958324418</v>
+        <v>0.09003581059497009</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D11" t="s">
         <v>40</v>
@@ -2985,13 +2985,13 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12">
-        <v>-2.424350385244781</v>
+        <v>-2.677573947594047</v>
       </c>
       <c r="B12">
-        <v>-0.450781171839332</v>
+        <v>0.11385003334467</v>
       </c>
       <c r="C12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D12" t="s">
         <v>40</v>
@@ -3005,13 +3005,13 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13">
-        <v>-2.915423722065669</v>
+        <v>-3.292429823902064</v>
       </c>
       <c r="B13">
-        <v>-0.498279763293111</v>
+        <v>-0.111147107555198</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D13" t="s">
         <v>40</v>
@@ -3025,13 +3025,13 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14">
-        <v>-3.397940008672037</v>
+        <v>-1.654097203523455</v>
       </c>
       <c r="B14">
-        <v>-0.289290911489516</v>
+        <v>-0.848791958324418</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14" t="s">
         <v>40</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15">
-        <v>-2.856985199745905</v>
+        <v>-2.424350385244781</v>
       </c>
       <c r="B15">
-        <v>-0.469319780554043</v>
+        <v>-0.450781171839332</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D15" t="s">
         <v>40</v>
@@ -3065,13 +3065,13 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16">
-        <v>-2.601192269796735</v>
+        <v>-2.915423722065669</v>
       </c>
       <c r="B16">
-        <v>-0.500649605959862</v>
+        <v>-0.498279763293111</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D16" t="s">
         <v>40</v>
@@ -3088,10 +3088,10 @@
         <v>-3.397940008672037</v>
       </c>
       <c r="B17">
-        <v>-0.315292202666391</v>
+        <v>-0.289290911489516</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D17" t="s">
         <v>40</v>
@@ -3105,13 +3105,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>-1.809080301087427</v>
+        <v>-2.856985199745905</v>
       </c>
       <c r="B18">
-        <v>0.445864153894975</v>
+        <v>-0.469319780554043</v>
       </c>
       <c r="C18">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D18" t="s">
         <v>40</v>
@@ -3125,13 +3125,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>-3.397940008672037</v>
+        <v>-2.601192269796735</v>
       </c>
       <c r="B19">
-        <v>0.0374450277689101</v>
+        <v>-0.500649605959862</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" t="s">
         <v>40</v>
@@ -3148,10 +3148,10 @@
         <v>-3.397940008672037</v>
       </c>
       <c r="B20">
-        <v>0.252937934475291</v>
+        <v>-0.315292202666391</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D20" t="s">
         <v>40</v>
@@ -3165,90 +3165,90 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>-1.740621171617036</v>
+        <v>-6.431798275933005</v>
+      </c>
+      <c r="B21">
+        <v>-0.280578645784238</v>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D21" t="s">
         <v>40</v>
       </c>
       <c r="E21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F21" t="s">
         <v>39</v>
-      </c>
-      <c r="G21">
-        <v>0.152099272842685</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>-3.397940008672037</v>
+        <v>-1.809080301087427</v>
+      </c>
+      <c r="B22">
+        <v>0.445864153894975</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D22" t="s">
         <v>40</v>
       </c>
       <c r="E22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F22" t="s">
         <v>39</v>
-      </c>
-      <c r="G22">
-        <v>-0.231610571295852</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>-2.983384452442823</v>
+        <v>-3.397940008672037</v>
+      </c>
+      <c r="B23">
+        <v>0.0374450277689101</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D23" t="s">
         <v>40</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F23" t="s">
         <v>39</v>
-      </c>
-      <c r="G23">
-        <v>0.432857865477844</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>-1.715163362357603</v>
+        <v>-3.397940008672037</v>
+      </c>
+      <c r="B24">
+        <v>0.252937934475291</v>
       </c>
       <c r="C24">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D24" t="s">
         <v>40</v>
       </c>
       <c r="E24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F24" t="s">
         <v>39</v>
-      </c>
-      <c r="G24">
-        <v>-0.156789341524764</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>-2.739451627363021</v>
+        <v>-1.740621171617036</v>
       </c>
       <c r="C25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D25" t="s">
         <v>40</v>
@@ -3260,7 +3260,7 @@
         <v>39</v>
       </c>
       <c r="G25">
-        <v>-0.226437746304586</v>
+        <v>0.152099272842685</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3268,7 +3268,7 @@
         <v>-3.397940008672037</v>
       </c>
       <c r="C26">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D26" t="s">
         <v>40</v>
@@ -3280,15 +3280,15 @@
         <v>39</v>
       </c>
       <c r="G26">
-        <v>0.641217139428201</v>
+        <v>-0.231610571295852</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>-2.785686102575601</v>
+        <v>-2.983384452442823</v>
       </c>
       <c r="C27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D27" t="s">
         <v>40</v>
@@ -3300,15 +3300,15 @@
         <v>39</v>
       </c>
       <c r="G27">
-        <v>0.270330686491062</v>
+        <v>0.432857865477844</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>-2.677573947594047</v>
+        <v>-6.431798275933005</v>
       </c>
       <c r="C28">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D28" t="s">
         <v>40</v>
@@ -3320,15 +3320,15 @@
         <v>39</v>
       </c>
       <c r="G28">
-        <v>-0.26095756179068</v>
+        <v>-0.0920954332798385</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>-3.292429823902064</v>
+        <v>-1.715163362357603</v>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D29" t="s">
         <v>40</v>
@@ -3340,12 +3340,12 @@
         <v>39</v>
       </c>
       <c r="G29">
-        <v>-0.103876306988104</v>
+        <v>-0.156789341524764</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>-1.654097203523455</v>
+        <v>-2.739451627363021</v>
       </c>
       <c r="C30">
         <v>5</v>
@@ -3360,15 +3360,15 @@
         <v>39</v>
       </c>
       <c r="G30">
-        <v>-0.275873944918795</v>
+        <v>-0.226437746304586</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>-2.424350385244781</v>
+        <v>-3.397940008672037</v>
       </c>
       <c r="C31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D31" t="s">
         <v>40</v>
@@ -3380,15 +3380,15 @@
         <v>39</v>
       </c>
       <c r="G31">
-        <v>-0.194736783370099</v>
+        <v>0.641217139428201</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>-2.915423722065669</v>
+        <v>-2.785686102575601</v>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D32" t="s">
         <v>40</v>
@@ -3400,15 +3400,15 @@
         <v>39</v>
       </c>
       <c r="G32">
-        <v>-0.435947499629224</v>
+        <v>0.270330686491062</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
-        <v>-3.397940008672037</v>
+        <v>-6.431798275933005</v>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D33" t="s">
         <v>40</v>
@@ -3420,15 +3420,15 @@
         <v>39</v>
       </c>
       <c r="G33">
-        <v>-0.0226367260223155</v>
+        <v>-0.592912423527445</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34">
-        <v>-2.856985199745905</v>
+        <v>-6.431798275933005</v>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D34" t="s">
         <v>40</v>
@@ -3440,15 +3440,15 @@
         <v>39</v>
       </c>
       <c r="G34">
-        <v>0.321846260044534</v>
+        <v>0.193129568653617</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
-        <v>-2.601192269796735</v>
+        <v>-2.677573947594047</v>
       </c>
       <c r="C35">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D35" t="s">
         <v>40</v>
@@ -3460,15 +3460,15 @@
         <v>39</v>
       </c>
       <c r="G35">
-        <v>-0.538346355052407</v>
+        <v>-0.26095756179068</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36">
-        <v>-3.397940008672037</v>
+        <v>-3.292429823902064</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D36" t="s">
         <v>40</v>
@@ -3480,15 +3480,15 @@
         <v>39</v>
       </c>
       <c r="G36">
-        <v>-0.375235682949177</v>
+        <v>-0.103876306988104</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
-        <v>-1.809080301087427</v>
+        <v>-1.654097203523455</v>
       </c>
       <c r="C37">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D37" t="s">
         <v>40</v>
@@ -3500,12 +3500,12 @@
         <v>39</v>
       </c>
       <c r="G37">
-        <v>-0.0398246823328143</v>
+        <v>-0.275873944918795</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
-        <v>-3.397940008672037</v>
+        <v>-2.424350385244781</v>
       </c>
       <c r="C38">
         <v>6</v>
@@ -3520,12 +3520,12 @@
         <v>39</v>
       </c>
       <c r="G38">
-        <v>-0.280611477050197</v>
+        <v>-0.194736783370099</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39">
-        <v>-3.397940008672037</v>
+        <v>-2.915423722065669</v>
       </c>
       <c r="C39">
         <v>7</v>
@@ -3540,32 +3540,32 @@
         <v>39</v>
       </c>
       <c r="G39">
-        <v>-0.103469471466357</v>
+        <v>-0.435947499629224</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
-        <v>-1.740621171617036</v>
+        <v>-3.397940008672037</v>
       </c>
       <c r="C40">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D40" t="s">
         <v>40</v>
       </c>
       <c r="E40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F40" t="s">
         <v>39</v>
       </c>
-      <c r="H40">
-        <v>1.25598601440942</v>
+      <c r="G40">
+        <v>-0.0226367260223155</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41">
-        <v>-3.397940008672037</v>
+        <v>-2.856985199745905</v>
       </c>
       <c r="C41">
         <v>3</v>
@@ -3574,141 +3574,141 @@
         <v>40</v>
       </c>
       <c r="E41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F41" t="s">
         <v>39</v>
       </c>
-      <c r="H41">
-        <v>0.345170395449932</v>
+      <c r="G41">
+        <v>0.321846260044534</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42">
-        <v>-2.983384452442823</v>
+        <v>-2.601192269796735</v>
       </c>
       <c r="C42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D42" t="s">
         <v>40</v>
       </c>
       <c r="E42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F42" t="s">
         <v>39</v>
       </c>
-      <c r="H42">
-        <v>1.33477019015128</v>
+      <c r="G42">
+        <v>-0.538346355052407</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43">
-        <v>-1.715163362357603</v>
+        <v>-3.397940008672037</v>
       </c>
       <c r="C43">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D43" t="s">
         <v>40</v>
       </c>
       <c r="E43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F43" t="s">
         <v>39</v>
       </c>
-      <c r="H43">
-        <v>0.217026514158214</v>
+      <c r="G43">
+        <v>-0.375235682949177</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44">
-        <v>-2.739451627363021</v>
+        <v>-6.431798275933005</v>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D44" t="s">
         <v>40</v>
       </c>
       <c r="E44" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F44" t="s">
         <v>39</v>
       </c>
-      <c r="H44">
-        <v>0.718869957920103</v>
+      <c r="G44">
+        <v>0.209242744018315</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45">
-        <v>-3.397940008672037</v>
+        <v>-1.809080301087427</v>
       </c>
       <c r="C45">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D45" t="s">
         <v>40</v>
       </c>
       <c r="E45" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F45" t="s">
         <v>39</v>
       </c>
-      <c r="H45">
-        <v>0.851468379115482</v>
+      <c r="G45">
+        <v>-0.0398246823328143</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46">
-        <v>-2.785686102575601</v>
+        <v>-3.397940008672037</v>
       </c>
       <c r="C46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D46" t="s">
         <v>40</v>
       </c>
       <c r="E46" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F46" t="s">
         <v>39</v>
       </c>
-      <c r="H46">
-        <v>1.34869015380779</v>
+      <c r="G46">
+        <v>-0.280611477050197</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47">
-        <v>-2.677573947594047</v>
+        <v>-3.397940008672037</v>
       </c>
       <c r="C47">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D47" t="s">
         <v>40</v>
       </c>
       <c r="E47" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F47" t="s">
         <v>39</v>
       </c>
-      <c r="H47">
-        <v>0.12735718259413</v>
+      <c r="G47">
+        <v>-0.103469471466357</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48">
-        <v>-3.292429823902064</v>
+        <v>-1.740621171617036</v>
       </c>
       <c r="C48">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D48" t="s">
         <v>40</v>
@@ -3720,15 +3720,15 @@
         <v>39</v>
       </c>
       <c r="H48">
-        <v>0.562789319485327</v>
+        <v>1.25598601440942</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49">
-        <v>-1.654097203523455</v>
+        <v>-3.397940008672037</v>
       </c>
       <c r="C49">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D49" t="s">
         <v>40</v>
@@ -3740,15 +3740,15 @@
         <v>39</v>
       </c>
       <c r="H49">
-        <v>0.908078815301368</v>
+        <v>0.345170395449932</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50">
-        <v>-2.424350385244781</v>
+        <v>-2.983384452442823</v>
       </c>
       <c r="C50">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D50" t="s">
         <v>40</v>
@@ -3760,15 +3760,15 @@
         <v>39</v>
       </c>
       <c r="H50">
-        <v>0.76283046315658</v>
+        <v>1.33477019015128</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51">
-        <v>-2.915423722065669</v>
+        <v>-6.431798275933005</v>
       </c>
       <c r="C51">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D51" t="s">
         <v>40</v>
@@ -3780,15 +3780,15 @@
         <v>39</v>
       </c>
       <c r="H51">
-        <v>1.27948724385031</v>
+        <v>0.677009496468449</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52">
-        <v>-3.397940008672037</v>
+        <v>-1.715163362357603</v>
       </c>
       <c r="C52">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D52" t="s">
         <v>40</v>
@@ -3800,15 +3800,15 @@
         <v>39</v>
       </c>
       <c r="H52">
-        <v>0.658101792156587</v>
+        <v>0.217026514158214</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53">
-        <v>-2.856985199745905</v>
+        <v>-2.739451627363021</v>
       </c>
       <c r="C53">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D53" t="s">
         <v>40</v>
@@ -3820,15 +3820,15 @@
         <v>39</v>
       </c>
       <c r="H53">
-        <v>1.12055697037774</v>
+        <v>0.718869957920103</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54">
-        <v>-2.601192269796735</v>
+        <v>-3.397940008672037</v>
       </c>
       <c r="C54">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D54" t="s">
         <v>40</v>
@@ -3840,15 +3840,15 @@
         <v>39</v>
       </c>
       <c r="H54">
-        <v>1.20812574981336</v>
+        <v>0.851468379115482</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55">
-        <v>-3.397940008672037</v>
+        <v>-2.785686102575601</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D55" t="s">
         <v>40</v>
@@ -3860,15 +3860,15 @@
         <v>39</v>
       </c>
       <c r="H55">
-        <v>0.810332909085531</v>
+        <v>1.34869015380779</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56">
-        <v>-1.809080301087427</v>
+        <v>-6.431798275933005</v>
       </c>
       <c r="C56">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D56" t="s">
         <v>40</v>
@@ -3880,15 +3880,15 @@
         <v>39</v>
       </c>
       <c r="H56">
-        <v>0.491935748883003</v>
+        <v>-0.410531667172635</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57">
-        <v>-3.397940008672037</v>
+        <v>-6.431798275933005</v>
       </c>
       <c r="C57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D57" t="s">
         <v>40</v>
@@ -3900,15 +3900,15 @@
         <v>39</v>
       </c>
       <c r="H57">
-        <v>0.464853923964679</v>
+        <v>0.579876266147953</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58">
-        <v>-3.397940008672037</v>
+        <v>-2.677573947594047</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D58" t="s">
         <v>40</v>
@@ -3920,532 +3920,535 @@
         <v>39</v>
       </c>
       <c r="H58">
-        <v>0.0149254334219611</v>
+        <v>0.12735718259413</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>-3.899629454882437</v>
-      </c>
-      <c r="B59">
-        <v>0.147344517689901</v>
+        <v>-3.292429823902064</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E59" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F59" t="s">
         <v>39</v>
+      </c>
+      <c r="H59">
+        <v>0.562789319485327</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
-        <v>-4.187086643357144</v>
-      </c>
-      <c r="B60">
-        <v>0.38408479759532</v>
+        <v>-1.654097203523455</v>
       </c>
       <c r="C60">
         <v>5</v>
       </c>
       <c r="D60" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E60" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F60" t="s">
         <v>39</v>
+      </c>
+      <c r="H60">
+        <v>0.908078815301368</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61">
-        <v>-4.259637310505756</v>
-      </c>
-      <c r="B61">
-        <v>0.379082481086608</v>
+        <v>-2.424350385244781</v>
       </c>
       <c r="C61">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D61" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E61" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F61" t="s">
         <v>39</v>
+      </c>
+      <c r="H61">
+        <v>0.76283046315658</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62">
-        <v>-3.920818753952375</v>
-      </c>
-      <c r="B62">
-        <v>-0.519883508724677</v>
+        <v>-2.915423722065669</v>
       </c>
       <c r="C62">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D62" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E62" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F62" t="s">
         <v>39</v>
+      </c>
+      <c r="H62">
+        <v>1.27948724385031</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63">
-        <v>-4.207608310501746</v>
-      </c>
-      <c r="B63">
-        <v>-0.450985563824396</v>
+        <v>-3.397940008672037</v>
       </c>
       <c r="C63">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D63" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E63" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F63" t="s">
         <v>39</v>
+      </c>
+      <c r="H63">
+        <v>0.658101792156587</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64">
-        <v>-3.913640169325252</v>
-      </c>
-      <c r="B64">
-        <v>0.209516616903352</v>
+        <v>-2.856985199745905</v>
       </c>
       <c r="C64">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D64" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E64" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F64" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="65" spans="1:7">
+      <c r="H64">
+        <v>1.12055697037774</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65">
-        <v>-4.070581074285707</v>
-      </c>
-      <c r="B65">
-        <v>-0.757605792680305</v>
+        <v>-2.601192269796735</v>
       </c>
       <c r="C65">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D65" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E65" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F65" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="66" spans="1:7">
+      <c r="H65">
+        <v>1.20812574981336</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66">
-        <v>-3.812479279163537</v>
-      </c>
-      <c r="B66">
-        <v>-0.159661571696305</v>
+        <v>-3.397940008672037</v>
       </c>
       <c r="C66">
         <v>2</v>
       </c>
       <c r="D66" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E66" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F66" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="67" spans="1:7">
+      <c r="H66">
+        <v>0.810332909085531</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67">
+        <v>-6.431798275933005</v>
+      </c>
+      <c r="C67">
+        <v>3</v>
+      </c>
+      <c r="D67" t="s">
+        <v>40</v>
+      </c>
+      <c r="E67" t="s">
+        <v>43</v>
+      </c>
+      <c r="F67" t="s">
+        <v>39</v>
+      </c>
+      <c r="H67">
+        <v>0.37996587290604</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68">
+        <v>-1.809080301087427</v>
+      </c>
+      <c r="C68">
+        <v>10</v>
+      </c>
+      <c r="D68" t="s">
+        <v>40</v>
+      </c>
+      <c r="E68" t="s">
+        <v>43</v>
+      </c>
+      <c r="F68" t="s">
+        <v>39</v>
+      </c>
+      <c r="H68">
+        <v>0.491935748883003</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69">
+        <v>-3.397940008672037</v>
+      </c>
+      <c r="C69">
+        <v>6</v>
+      </c>
+      <c r="D69" t="s">
+        <v>40</v>
+      </c>
+      <c r="E69" t="s">
+        <v>43</v>
+      </c>
+      <c r="F69" t="s">
+        <v>39</v>
+      </c>
+      <c r="H69">
+        <v>0.464853923964679</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70">
+        <v>-3.397940008672037</v>
+      </c>
+      <c r="C70">
+        <v>7</v>
+      </c>
+      <c r="D70" t="s">
+        <v>40</v>
+      </c>
+      <c r="E70" t="s">
+        <v>43</v>
+      </c>
+      <c r="F70" t="s">
+        <v>39</v>
+      </c>
+      <c r="H70">
+        <v>0.0149254334219611</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71">
+        <v>-3.899629454882437</v>
+      </c>
+      <c r="B71">
+        <v>0.147344517689901</v>
+      </c>
+      <c r="C71">
+        <v>7</v>
+      </c>
+      <c r="D71" t="s">
+        <v>44</v>
+      </c>
+      <c r="E71" t="s">
+        <v>41</v>
+      </c>
+      <c r="F71" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72">
+        <v>-4.187086643357144</v>
+      </c>
+      <c r="B72">
+        <v>0.38408479759532</v>
+      </c>
+      <c r="C72">
+        <v>5</v>
+      </c>
+      <c r="D72" t="s">
+        <v>44</v>
+      </c>
+      <c r="E72" t="s">
+        <v>41</v>
+      </c>
+      <c r="F72" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73">
+        <v>-4.259637310505756</v>
+      </c>
+      <c r="B73">
+        <v>0.379082481086608</v>
+      </c>
+      <c r="C73">
+        <v>8</v>
+      </c>
+      <c r="D73" t="s">
+        <v>44</v>
+      </c>
+      <c r="E73" t="s">
+        <v>41</v>
+      </c>
+      <c r="F73" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74">
+        <v>-3.920818753952375</v>
+      </c>
+      <c r="B74">
+        <v>-0.519883508724677</v>
+      </c>
+      <c r="C74">
+        <v>3</v>
+      </c>
+      <c r="D74" t="s">
+        <v>44</v>
+      </c>
+      <c r="E74" t="s">
+        <v>41</v>
+      </c>
+      <c r="F74" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75">
+        <v>-4.207608310501746</v>
+      </c>
+      <c r="B75">
+        <v>-0.450985563824396</v>
+      </c>
+      <c r="C75">
+        <v>8</v>
+      </c>
+      <c r="D75" t="s">
+        <v>44</v>
+      </c>
+      <c r="E75" t="s">
+        <v>41</v>
+      </c>
+      <c r="F75" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76">
+        <v>-3.913640169325252</v>
+      </c>
+      <c r="B76">
+        <v>0.209516616903352</v>
+      </c>
+      <c r="C76">
+        <v>8</v>
+      </c>
+      <c r="D76" t="s">
+        <v>44</v>
+      </c>
+      <c r="E76" t="s">
+        <v>41</v>
+      </c>
+      <c r="F76" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77">
+        <v>-4.070581074285707</v>
+      </c>
+      <c r="B77">
+        <v>-0.757605792680305</v>
+      </c>
+      <c r="C77">
+        <v>6</v>
+      </c>
+      <c r="D77" t="s">
+        <v>44</v>
+      </c>
+      <c r="E77" t="s">
+        <v>41</v>
+      </c>
+      <c r="F77" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78">
+        <v>-6.431798275933005</v>
+      </c>
+      <c r="B78">
+        <v>-0.133518059229311</v>
+      </c>
+      <c r="C78">
+        <v>5</v>
+      </c>
+      <c r="D78" t="s">
+        <v>44</v>
+      </c>
+      <c r="E78" t="s">
+        <v>41</v>
+      </c>
+      <c r="F78" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79">
+        <v>-3.812479279163537</v>
+      </c>
+      <c r="B79">
+        <v>-0.159661571696305</v>
+      </c>
+      <c r="C79">
+        <v>2</v>
+      </c>
+      <c r="D79" t="s">
+        <v>44</v>
+      </c>
+      <c r="E79" t="s">
+        <v>41</v>
+      </c>
+      <c r="F79" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80">
         <v>-3.300162274132754</v>
       </c>
-      <c r="B67">
+      <c r="B80">
         <v>0.458709467867156</v>
       </c>
-      <c r="C67">
+      <c r="C80">
         <v>6</v>
       </c>
-      <c r="D67" t="s">
-        <v>44</v>
-      </c>
-      <c r="E67" t="s">
-        <v>41</v>
-      </c>
-      <c r="F67" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68">
+      <c r="D80" t="s">
+        <v>44</v>
+      </c>
+      <c r="E80" t="s">
+        <v>41</v>
+      </c>
+      <c r="F80" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81">
         <v>-3.978810700930062</v>
       </c>
-      <c r="B68">
+      <c r="B81">
         <v>-0.280226169024453</v>
       </c>
-      <c r="C68">
+      <c r="C81">
         <v>6</v>
       </c>
-      <c r="D68" t="s">
-        <v>44</v>
-      </c>
-      <c r="E68" t="s">
-        <v>41</v>
-      </c>
-      <c r="F68" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69">
+      <c r="D81" t="s">
+        <v>44</v>
+      </c>
+      <c r="E81" t="s">
+        <v>41</v>
+      </c>
+      <c r="F81" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82">
         <v>-4.431798275933005</v>
       </c>
-      <c r="B69">
+      <c r="B82">
         <v>-0.0703934692254202</v>
       </c>
-      <c r="C69">
+      <c r="C82">
         <v>7</v>
       </c>
-      <c r="D69" t="s">
-        <v>44</v>
-      </c>
-      <c r="E69" t="s">
-        <v>41</v>
-      </c>
-      <c r="F69" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70">
+      <c r="D82" t="s">
+        <v>44</v>
+      </c>
+      <c r="E82" t="s">
+        <v>41</v>
+      </c>
+      <c r="F82" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83">
         <v>-3.302770657240282</v>
       </c>
-      <c r="B70">
+      <c r="B83">
         <v>0.0640783976204007</v>
       </c>
-      <c r="C70">
+      <c r="C83">
         <v>1</v>
       </c>
-      <c r="D70" t="s">
-        <v>44</v>
-      </c>
-      <c r="E70" t="s">
-        <v>41</v>
-      </c>
-      <c r="F70" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71">
+      <c r="D83" t="s">
+        <v>44</v>
+      </c>
+      <c r="E83" t="s">
+        <v>41</v>
+      </c>
+      <c r="F83" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84">
         <v>-4.387216143280265</v>
       </c>
-      <c r="B71">
+      <c r="B84">
         <v>0.281112876926168</v>
       </c>
-      <c r="C71">
+      <c r="C84">
         <v>8</v>
       </c>
-      <c r="D71" t="s">
-        <v>44</v>
-      </c>
-      <c r="E71" t="s">
-        <v>41</v>
-      </c>
-      <c r="F71" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
-      <c r="A72">
+      <c r="D84" t="s">
+        <v>44</v>
+      </c>
+      <c r="E84" t="s">
+        <v>41</v>
+      </c>
+      <c r="F84" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85">
         <v>-4.283996656365201</v>
       </c>
-      <c r="B72">
+      <c r="B85">
         <v>0.276024526742628</v>
-      </c>
-      <c r="C72">
-        <v>6</v>
-      </c>
-      <c r="D72" t="s">
-        <v>44</v>
-      </c>
-      <c r="E72" t="s">
-        <v>41</v>
-      </c>
-      <c r="F72" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
-      <c r="A73">
-        <v>-4.09151498112135</v>
-      </c>
-      <c r="B73">
-        <v>-0.234335334102896</v>
-      </c>
-      <c r="C73">
-        <v>6</v>
-      </c>
-      <c r="D73" t="s">
-        <v>44</v>
-      </c>
-      <c r="E73" t="s">
-        <v>41</v>
-      </c>
-      <c r="F73" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
-      <c r="A74">
-        <v>-3.847711655616943</v>
-      </c>
-      <c r="B74">
-        <v>0.989088062543571</v>
-      </c>
-      <c r="C74">
-        <v>5</v>
-      </c>
-      <c r="D74" t="s">
-        <v>44</v>
-      </c>
-      <c r="E74" t="s">
-        <v>41</v>
-      </c>
-      <c r="F74" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
-      <c r="A75">
-        <v>-4.142667503568732</v>
-      </c>
-      <c r="B75">
-        <v>0.187127525448045</v>
-      </c>
-      <c r="C75">
-        <v>1</v>
-      </c>
-      <c r="D75" t="s">
-        <v>44</v>
-      </c>
-      <c r="E75" t="s">
-        <v>41</v>
-      </c>
-      <c r="F75" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
-      <c r="A76">
-        <v>-3.899629454882437</v>
-      </c>
-      <c r="C76">
-        <v>7</v>
-      </c>
-      <c r="D76" t="s">
-        <v>44</v>
-      </c>
-      <c r="E76" t="s">
-        <v>42</v>
-      </c>
-      <c r="F76" t="s">
-        <v>39</v>
-      </c>
-      <c r="G76">
-        <v>-0.0375410732186684</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
-      <c r="A77">
-        <v>-4.187086643357144</v>
-      </c>
-      <c r="C77">
-        <v>5</v>
-      </c>
-      <c r="D77" t="s">
-        <v>44</v>
-      </c>
-      <c r="E77" t="s">
-        <v>42</v>
-      </c>
-      <c r="F77" t="s">
-        <v>39</v>
-      </c>
-      <c r="G77">
-        <v>-0.722357967664132</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78">
-        <v>-4.259637310505756</v>
-      </c>
-      <c r="C78">
-        <v>8</v>
-      </c>
-      <c r="D78" t="s">
-        <v>44</v>
-      </c>
-      <c r="E78" t="s">
-        <v>42</v>
-      </c>
-      <c r="F78" t="s">
-        <v>39</v>
-      </c>
-      <c r="G78">
-        <v>-0.138869177521999</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
-      <c r="A79">
-        <v>-3.920818753952375</v>
-      </c>
-      <c r="C79">
-        <v>3</v>
-      </c>
-      <c r="D79" t="s">
-        <v>44</v>
-      </c>
-      <c r="E79" t="s">
-        <v>42</v>
-      </c>
-      <c r="F79" t="s">
-        <v>39</v>
-      </c>
-      <c r="G79">
-        <v>-0.44258814294427</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
-      <c r="A80">
-        <v>-4.207608310501746</v>
-      </c>
-      <c r="C80">
-        <v>8</v>
-      </c>
-      <c r="D80" t="s">
-        <v>44</v>
-      </c>
-      <c r="E80" t="s">
-        <v>42</v>
-      </c>
-      <c r="F80" t="s">
-        <v>39</v>
-      </c>
-      <c r="G80">
-        <v>-0.570727541979385</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8">
-      <c r="A81">
-        <v>-3.913640169325252</v>
-      </c>
-      <c r="C81">
-        <v>8</v>
-      </c>
-      <c r="D81" t="s">
-        <v>44</v>
-      </c>
-      <c r="E81" t="s">
-        <v>42</v>
-      </c>
-      <c r="F81" t="s">
-        <v>39</v>
-      </c>
-      <c r="G81">
-        <v>-0.0562040244611147</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8">
-      <c r="A82">
-        <v>-4.070581074285707</v>
-      </c>
-      <c r="C82">
-        <v>6</v>
-      </c>
-      <c r="D82" t="s">
-        <v>44</v>
-      </c>
-      <c r="E82" t="s">
-        <v>42</v>
-      </c>
-      <c r="F82" t="s">
-        <v>39</v>
-      </c>
-      <c r="G82">
-        <v>-0.278629251082361</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8">
-      <c r="A83">
-        <v>-3.812479279163537</v>
-      </c>
-      <c r="C83">
-        <v>2</v>
-      </c>
-      <c r="D83" t="s">
-        <v>44</v>
-      </c>
-      <c r="E83" t="s">
-        <v>42</v>
-      </c>
-      <c r="F83" t="s">
-        <v>39</v>
-      </c>
-      <c r="G83">
-        <v>-0.613111334486333</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
-      <c r="A84">
-        <v>-3.300162274132754</v>
-      </c>
-      <c r="C84">
-        <v>6</v>
-      </c>
-      <c r="D84" t="s">
-        <v>44</v>
-      </c>
-      <c r="E84" t="s">
-        <v>42</v>
-      </c>
-      <c r="F84" t="s">
-        <v>39</v>
-      </c>
-      <c r="G84">
-        <v>0.174728008874928</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
-      <c r="A85">
-        <v>-3.978810700930062</v>
       </c>
       <c r="C85">
         <v>6</v>
@@ -4454,238 +4457,235 @@
         <v>44</v>
       </c>
       <c r="E85" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F85" t="s">
         <v>39</v>
       </c>
-      <c r="G85">
-        <v>-0.29463217049043</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
+    </row>
+    <row r="86" spans="1:7">
       <c r="A86">
-        <v>-4.431798275933005</v>
+        <v>-4.09151498112135</v>
+      </c>
+      <c r="B86">
+        <v>-0.234335334102896</v>
       </c>
       <c r="C86">
+        <v>6</v>
+      </c>
+      <c r="D86" t="s">
+        <v>44</v>
+      </c>
+      <c r="E86" t="s">
+        <v>41</v>
+      </c>
+      <c r="F86" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87">
+        <v>-6.431798275933005</v>
+      </c>
+      <c r="B87">
+        <v>-0.498787596352037</v>
+      </c>
+      <c r="C87">
+        <v>3</v>
+      </c>
+      <c r="D87" t="s">
+        <v>44</v>
+      </c>
+      <c r="E87" t="s">
+        <v>41</v>
+      </c>
+      <c r="F87" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88">
+        <v>-3.847711655616943</v>
+      </c>
+      <c r="B88">
+        <v>0.989088062543571</v>
+      </c>
+      <c r="C88">
+        <v>5</v>
+      </c>
+      <c r="D88" t="s">
+        <v>44</v>
+      </c>
+      <c r="E88" t="s">
+        <v>41</v>
+      </c>
+      <c r="F88" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89">
+        <v>-4.142667503568732</v>
+      </c>
+      <c r="B89">
+        <v>0.187127525448045</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+      <c r="D89" t="s">
+        <v>44</v>
+      </c>
+      <c r="E89" t="s">
+        <v>41</v>
+      </c>
+      <c r="F89" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90">
+        <v>-6.431798275933005</v>
+      </c>
+      <c r="B90">
+        <v>-0.113775944249812</v>
+      </c>
+      <c r="C90">
+        <v>3</v>
+      </c>
+      <c r="D90" t="s">
+        <v>44</v>
+      </c>
+      <c r="E90" t="s">
+        <v>41</v>
+      </c>
+      <c r="F90" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91">
+        <v>-6.431798275933005</v>
+      </c>
+      <c r="B91">
+        <v>0.319328267663351</v>
+      </c>
+      <c r="C91">
+        <v>4</v>
+      </c>
+      <c r="D91" t="s">
+        <v>44</v>
+      </c>
+      <c r="E91" t="s">
+        <v>41</v>
+      </c>
+      <c r="F91" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92">
+        <v>-3.899629454882437</v>
+      </c>
+      <c r="C92">
         <v>7</v>
       </c>
-      <c r="D86" t="s">
-        <v>44</v>
-      </c>
-      <c r="E86" t="s">
-        <v>42</v>
-      </c>
-      <c r="F86" t="s">
-        <v>39</v>
-      </c>
-      <c r="G86">
-        <v>-0.34631970130354</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
-      <c r="A87">
-        <v>-3.302770657240282</v>
-      </c>
-      <c r="C87">
-        <v>1</v>
-      </c>
-      <c r="D87" t="s">
-        <v>44</v>
-      </c>
-      <c r="E87" t="s">
-        <v>42</v>
-      </c>
-      <c r="F87" t="s">
-        <v>39</v>
-      </c>
-      <c r="G87">
-        <v>-0.345390972310118</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
-      <c r="A88">
-        <v>-4.387216143280265</v>
-      </c>
-      <c r="C88">
+      <c r="D92" t="s">
+        <v>44</v>
+      </c>
+      <c r="E92" t="s">
+        <v>42</v>
+      </c>
+      <c r="F92" t="s">
+        <v>39</v>
+      </c>
+      <c r="G92">
+        <v>-0.0375410732186684</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93">
+        <v>-4.187086643357144</v>
+      </c>
+      <c r="C93">
+        <v>5</v>
+      </c>
+      <c r="D93" t="s">
+        <v>44</v>
+      </c>
+      <c r="E93" t="s">
+        <v>42</v>
+      </c>
+      <c r="F93" t="s">
+        <v>39</v>
+      </c>
+      <c r="G93">
+        <v>-0.722357967664132</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94">
+        <v>-4.259637310505756</v>
+      </c>
+      <c r="C94">
         <v>8</v>
       </c>
-      <c r="D88" t="s">
-        <v>44</v>
-      </c>
-      <c r="E88" t="s">
-        <v>42</v>
-      </c>
-      <c r="F88" t="s">
-        <v>39</v>
-      </c>
-      <c r="G88">
-        <v>-0.0427390785784223</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
-      <c r="A89">
-        <v>-4.283996656365201</v>
-      </c>
-      <c r="C89">
-        <v>6</v>
-      </c>
-      <c r="D89" t="s">
-        <v>44</v>
-      </c>
-      <c r="E89" t="s">
-        <v>42</v>
-      </c>
-      <c r="F89" t="s">
-        <v>39</v>
-      </c>
-      <c r="G89">
-        <v>0.030826399608212</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8">
-      <c r="A90">
-        <v>-4.09151498112135</v>
-      </c>
-      <c r="C90">
-        <v>6</v>
-      </c>
-      <c r="D90" t="s">
-        <v>44</v>
-      </c>
-      <c r="E90" t="s">
-        <v>42</v>
-      </c>
-      <c r="F90" t="s">
-        <v>39</v>
-      </c>
-      <c r="G90">
-        <v>-0.505226847445966</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8">
-      <c r="A91">
-        <v>-3.847711655616943</v>
-      </c>
-      <c r="C91">
-        <v>5</v>
-      </c>
-      <c r="D91" t="s">
-        <v>44</v>
-      </c>
-      <c r="E91" t="s">
-        <v>42</v>
-      </c>
-      <c r="F91" t="s">
-        <v>39</v>
-      </c>
-      <c r="G91">
-        <v>-0.0411373088330105</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8">
-      <c r="A92">
-        <v>-4.142667503568732</v>
-      </c>
-      <c r="C92">
-        <v>1</v>
-      </c>
-      <c r="D92" t="s">
-        <v>44</v>
-      </c>
-      <c r="E92" t="s">
-        <v>42</v>
-      </c>
-      <c r="F92" t="s">
-        <v>39</v>
-      </c>
-      <c r="G92">
-        <v>-0.6827604092071849</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8">
-      <c r="A93">
-        <v>-3.899629454882437</v>
-      </c>
-      <c r="C93">
-        <v>7</v>
-      </c>
-      <c r="D93" t="s">
-        <v>44</v>
-      </c>
-      <c r="E93" t="s">
-        <v>43</v>
-      </c>
-      <c r="F93" t="s">
-        <v>39</v>
-      </c>
-      <c r="H93">
-        <v>1.62060979966916</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8">
-      <c r="A94">
-        <v>-4.187086643357144</v>
-      </c>
-      <c r="C94">
-        <v>5</v>
-      </c>
       <c r="D94" t="s">
         <v>44</v>
       </c>
       <c r="E94" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F94" t="s">
         <v>39</v>
       </c>
-      <c r="H94">
-        <v>0.655106526642534</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8">
+      <c r="G94">
+        <v>-0.138869177521999</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
       <c r="A95">
-        <v>-4.259637310505756</v>
+        <v>-3.920818753952375</v>
       </c>
       <c r="C95">
+        <v>3</v>
+      </c>
+      <c r="D95" t="s">
+        <v>44</v>
+      </c>
+      <c r="E95" t="s">
+        <v>42</v>
+      </c>
+      <c r="F95" t="s">
+        <v>39</v>
+      </c>
+      <c r="G95">
+        <v>-0.44258814294427</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96">
+        <v>-4.207608310501746</v>
+      </c>
+      <c r="C96">
         <v>8</v>
       </c>
-      <c r="D95" t="s">
-        <v>44</v>
-      </c>
-      <c r="E95" t="s">
-        <v>43</v>
-      </c>
-      <c r="F95" t="s">
-        <v>39</v>
-      </c>
-      <c r="H95">
-        <v>0.9557880831743329</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8">
-      <c r="A96">
-        <v>-3.920818753952375</v>
-      </c>
-      <c r="C96">
-        <v>3</v>
-      </c>
       <c r="D96" t="s">
         <v>44</v>
       </c>
       <c r="E96" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F96" t="s">
         <v>39</v>
       </c>
-      <c r="H96">
-        <v>1.36921519828388</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
+      <c r="G96">
+        <v>-0.570727541979385</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
       <c r="A97">
-        <v>-4.207608310501746</v>
+        <v>-3.913640169325252</v>
       </c>
       <c r="C97">
         <v>8</v>
@@ -4694,56 +4694,56 @@
         <v>44</v>
       </c>
       <c r="E97" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F97" t="s">
         <v>39</v>
       </c>
-      <c r="H97">
-        <v>0.0204880793857893</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8">
+      <c r="G97">
+        <v>-0.0562040244611147</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
       <c r="A98">
-        <v>-3.913640169325252</v>
+        <v>-4.070581074285707</v>
       </c>
       <c r="C98">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D98" t="s">
         <v>44</v>
       </c>
       <c r="E98" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F98" t="s">
         <v>39</v>
       </c>
-      <c r="H98">
-        <v>0.420649580268788</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8">
+      <c r="G98">
+        <v>-0.278629251082361</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
       <c r="A99">
-        <v>-4.070581074285707</v>
+        <v>-6.431798275933005</v>
       </c>
       <c r="C99">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D99" t="s">
         <v>44</v>
       </c>
       <c r="E99" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F99" t="s">
         <v>39</v>
       </c>
-      <c r="H99">
-        <v>0.0546308414497147</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8">
+      <c r="G99">
+        <v>-0.290801242327032</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
       <c r="A100">
         <v>-3.812479279163537</v>
       </c>
@@ -4754,16 +4754,16 @@
         <v>44</v>
       </c>
       <c r="E100" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F100" t="s">
         <v>39</v>
       </c>
-      <c r="H100">
-        <v>0.295676022395305</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8">
+      <c r="G100">
+        <v>-0.613111334486333</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
       <c r="A101">
         <v>-3.300162274132754</v>
       </c>
@@ -4774,16 +4774,16 @@
         <v>44</v>
       </c>
       <c r="E101" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F101" t="s">
         <v>39</v>
       </c>
-      <c r="H101">
-        <v>1.27631474917799</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8">
+      <c r="G101">
+        <v>0.174728008874928</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
       <c r="A102">
         <v>-3.978810700930062</v>
       </c>
@@ -4794,16 +4794,16 @@
         <v>44</v>
       </c>
       <c r="E102" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F102" t="s">
         <v>39</v>
       </c>
-      <c r="H102">
-        <v>0.154875596189611</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8">
+      <c r="G102">
+        <v>-0.29463217049043</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
       <c r="A103">
         <v>-4.431798275933005</v>
       </c>
@@ -4814,16 +4814,16 @@
         <v>44</v>
       </c>
       <c r="E103" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F103" t="s">
         <v>39</v>
       </c>
-      <c r="H103">
-        <v>0.44346490965271</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8">
+      <c r="G103">
+        <v>-0.34631970130354</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
       <c r="A104">
         <v>-3.302770657240282</v>
       </c>
@@ -4834,16 +4834,16 @@
         <v>44</v>
       </c>
       <c r="E104" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F104" t="s">
         <v>39</v>
       </c>
-      <c r="H104">
-        <v>1.41730933320219</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8">
+      <c r="G104">
+        <v>-0.345390972310118</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
       <c r="A105">
         <v>-4.387216143280265</v>
       </c>
@@ -4854,16 +4854,16 @@
         <v>44</v>
       </c>
       <c r="E105" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F105" t="s">
         <v>39</v>
       </c>
-      <c r="H105">
-        <v>1.1645600586537</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8">
+      <c r="G105">
+        <v>-0.0427390785784223</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
       <c r="A106">
         <v>-4.283996656365201</v>
       </c>
@@ -4874,16 +4874,16 @@
         <v>44</v>
       </c>
       <c r="E106" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F106" t="s">
         <v>39</v>
       </c>
-      <c r="H106">
-        <v>0.662402394834722</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8">
+      <c r="G106">
+        <v>0.030826399608212</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
       <c r="A107">
         <v>-4.09151498112135</v>
       </c>
@@ -4894,53 +4894,533 @@
         <v>44</v>
       </c>
       <c r="E107" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F107" t="s">
         <v>39</v>
       </c>
-      <c r="H107">
+      <c r="G107">
+        <v>-0.505226847445966</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108">
+        <v>-6.431798275933005</v>
+      </c>
+      <c r="C108">
+        <v>3</v>
+      </c>
+      <c r="D108" t="s">
+        <v>44</v>
+      </c>
+      <c r="E108" t="s">
+        <v>42</v>
+      </c>
+      <c r="F108" t="s">
+        <v>39</v>
+      </c>
+      <c r="G108">
+        <v>-0.964590502091222</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109">
+        <v>-3.847711655616943</v>
+      </c>
+      <c r="C109">
+        <v>5</v>
+      </c>
+      <c r="D109" t="s">
+        <v>44</v>
+      </c>
+      <c r="E109" t="s">
+        <v>42</v>
+      </c>
+      <c r="F109" t="s">
+        <v>39</v>
+      </c>
+      <c r="G109">
+        <v>-0.0411373088330105</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110">
+        <v>-4.142667503568732</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+      <c r="D110" t="s">
+        <v>44</v>
+      </c>
+      <c r="E110" t="s">
+        <v>42</v>
+      </c>
+      <c r="F110" t="s">
+        <v>39</v>
+      </c>
+      <c r="G110">
+        <v>-0.6827604092071849</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111">
+        <v>-6.431798275933005</v>
+      </c>
+      <c r="C111">
+        <v>3</v>
+      </c>
+      <c r="D111" t="s">
+        <v>44</v>
+      </c>
+      <c r="E111" t="s">
+        <v>42</v>
+      </c>
+      <c r="F111" t="s">
+        <v>39</v>
+      </c>
+      <c r="G111">
+        <v>-0.318577607712004</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112">
+        <v>-6.431798275933005</v>
+      </c>
+      <c r="C112">
+        <v>4</v>
+      </c>
+      <c r="D112" t="s">
+        <v>44</v>
+      </c>
+      <c r="E112" t="s">
+        <v>42</v>
+      </c>
+      <c r="F112" t="s">
+        <v>39</v>
+      </c>
+      <c r="G112">
+        <v>0.0511641223791905</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113">
+        <v>-3.899629454882437</v>
+      </c>
+      <c r="C113">
+        <v>7</v>
+      </c>
+      <c r="D113" t="s">
+        <v>44</v>
+      </c>
+      <c r="E113" t="s">
+        <v>43</v>
+      </c>
+      <c r="F113" t="s">
+        <v>39</v>
+      </c>
+      <c r="H113">
+        <v>1.62060979966916</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114">
+        <v>-4.187086643357144</v>
+      </c>
+      <c r="C114">
+        <v>5</v>
+      </c>
+      <c r="D114" t="s">
+        <v>44</v>
+      </c>
+      <c r="E114" t="s">
+        <v>43</v>
+      </c>
+      <c r="F114" t="s">
+        <v>39</v>
+      </c>
+      <c r="H114">
+        <v>0.655106526642534</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115">
+        <v>-4.259637310505756</v>
+      </c>
+      <c r="C115">
+        <v>8</v>
+      </c>
+      <c r="D115" t="s">
+        <v>44</v>
+      </c>
+      <c r="E115" t="s">
+        <v>43</v>
+      </c>
+      <c r="F115" t="s">
+        <v>39</v>
+      </c>
+      <c r="H115">
+        <v>0.9557880831743329</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116">
+        <v>-3.920818753952375</v>
+      </c>
+      <c r="C116">
+        <v>3</v>
+      </c>
+      <c r="D116" t="s">
+        <v>44</v>
+      </c>
+      <c r="E116" t="s">
+        <v>43</v>
+      </c>
+      <c r="F116" t="s">
+        <v>39</v>
+      </c>
+      <c r="H116">
+        <v>1.36921519828388</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117">
+        <v>-4.207608310501746</v>
+      </c>
+      <c r="C117">
+        <v>8</v>
+      </c>
+      <c r="D117" t="s">
+        <v>44</v>
+      </c>
+      <c r="E117" t="s">
+        <v>43</v>
+      </c>
+      <c r="F117" t="s">
+        <v>39</v>
+      </c>
+      <c r="H117">
+        <v>0.0204880793857893</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118">
+        <v>-3.913640169325252</v>
+      </c>
+      <c r="C118">
+        <v>8</v>
+      </c>
+      <c r="D118" t="s">
+        <v>44</v>
+      </c>
+      <c r="E118" t="s">
+        <v>43</v>
+      </c>
+      <c r="F118" t="s">
+        <v>39</v>
+      </c>
+      <c r="H118">
+        <v>0.420649580268788</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119">
+        <v>-4.070581074285707</v>
+      </c>
+      <c r="C119">
+        <v>6</v>
+      </c>
+      <c r="D119" t="s">
+        <v>44</v>
+      </c>
+      <c r="E119" t="s">
+        <v>43</v>
+      </c>
+      <c r="F119" t="s">
+        <v>39</v>
+      </c>
+      <c r="H119">
+        <v>0.0546308414497147</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120">
+        <v>-6.431798275933005</v>
+      </c>
+      <c r="C120">
+        <v>5</v>
+      </c>
+      <c r="D120" t="s">
+        <v>44</v>
+      </c>
+      <c r="E120" t="s">
+        <v>43</v>
+      </c>
+      <c r="F120" t="s">
+        <v>39</v>
+      </c>
+      <c r="H120">
+        <v>0.613234709926969</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121">
+        <v>-3.812479279163537</v>
+      </c>
+      <c r="C121">
+        <v>2</v>
+      </c>
+      <c r="D121" t="s">
+        <v>44</v>
+      </c>
+      <c r="E121" t="s">
+        <v>43</v>
+      </c>
+      <c r="F121" t="s">
+        <v>39</v>
+      </c>
+      <c r="H121">
+        <v>0.295676022395305</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122">
+        <v>-3.300162274132754</v>
+      </c>
+      <c r="C122">
+        <v>6</v>
+      </c>
+      <c r="D122" t="s">
+        <v>44</v>
+      </c>
+      <c r="E122" t="s">
+        <v>43</v>
+      </c>
+      <c r="F122" t="s">
+        <v>39</v>
+      </c>
+      <c r="H122">
+        <v>1.27631474917799</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123">
+        <v>-3.978810700930062</v>
+      </c>
+      <c r="C123">
+        <v>6</v>
+      </c>
+      <c r="D123" t="s">
+        <v>44</v>
+      </c>
+      <c r="E123" t="s">
+        <v>43</v>
+      </c>
+      <c r="F123" t="s">
+        <v>39</v>
+      </c>
+      <c r="H123">
+        <v>0.154875596189611</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124">
+        <v>-4.431798275933005</v>
+      </c>
+      <c r="C124">
+        <v>7</v>
+      </c>
+      <c r="D124" t="s">
+        <v>44</v>
+      </c>
+      <c r="E124" t="s">
+        <v>43</v>
+      </c>
+      <c r="F124" t="s">
+        <v>39</v>
+      </c>
+      <c r="H124">
+        <v>0.44346490965271</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125">
+        <v>-3.302770657240282</v>
+      </c>
+      <c r="C125">
+        <v>1</v>
+      </c>
+      <c r="D125" t="s">
+        <v>44</v>
+      </c>
+      <c r="E125" t="s">
+        <v>43</v>
+      </c>
+      <c r="F125" t="s">
+        <v>39</v>
+      </c>
+      <c r="H125">
+        <v>1.41730933320219</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126">
+        <v>-4.387216143280265</v>
+      </c>
+      <c r="C126">
+        <v>8</v>
+      </c>
+      <c r="D126" t="s">
+        <v>44</v>
+      </c>
+      <c r="E126" t="s">
+        <v>43</v>
+      </c>
+      <c r="F126" t="s">
+        <v>39</v>
+      </c>
+      <c r="H126">
+        <v>1.1645600586537</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127">
+        <v>-4.283996656365201</v>
+      </c>
+      <c r="C127">
+        <v>6</v>
+      </c>
+      <c r="D127" t="s">
+        <v>44</v>
+      </c>
+      <c r="E127" t="s">
+        <v>43</v>
+      </c>
+      <c r="F127" t="s">
+        <v>39</v>
+      </c>
+      <c r="H127">
+        <v>0.662402394834722</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128">
+        <v>-4.09151498112135</v>
+      </c>
+      <c r="C128">
+        <v>6</v>
+      </c>
+      <c r="D128" t="s">
+        <v>44</v>
+      </c>
+      <c r="E128" t="s">
+        <v>43</v>
+      </c>
+      <c r="F128" t="s">
+        <v>39</v>
+      </c>
+      <c r="H128">
         <v>-0.222014068177802</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
-      <c r="A108">
+    <row r="129" spans="1:8">
+      <c r="A129">
+        <v>-6.431798275933005</v>
+      </c>
+      <c r="C129">
+        <v>3</v>
+      </c>
+      <c r="D129" t="s">
+        <v>44</v>
+      </c>
+      <c r="E129" t="s">
+        <v>43</v>
+      </c>
+      <c r="F129" t="s">
+        <v>39</v>
+      </c>
+      <c r="H129">
+        <v>0.365155123240234</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130">
         <v>-3.847711655616943</v>
       </c>
-      <c r="C108">
+      <c r="C130">
         <v>5</v>
       </c>
-      <c r="D108" t="s">
-        <v>44</v>
-      </c>
-      <c r="E108" t="s">
-        <v>43</v>
-      </c>
-      <c r="F108" t="s">
-        <v>39</v>
-      </c>
-      <c r="H108">
+      <c r="D130" t="s">
+        <v>44</v>
+      </c>
+      <c r="E130" t="s">
+        <v>43</v>
+      </c>
+      <c r="F130" t="s">
+        <v>39</v>
+      </c>
+      <c r="H130">
         <v>0.260154059022513</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
-      <c r="A109">
+    <row r="131" spans="1:8">
+      <c r="A131">
         <v>-4.142667503568732</v>
       </c>
-      <c r="C109">
+      <c r="C131">
         <v>1</v>
       </c>
-      <c r="D109" t="s">
-        <v>44</v>
-      </c>
-      <c r="E109" t="s">
-        <v>43</v>
-      </c>
-      <c r="F109" t="s">
-        <v>39</v>
-      </c>
-      <c r="H109">
+      <c r="D131" t="s">
+        <v>44</v>
+      </c>
+      <c r="E131" t="s">
+        <v>43</v>
+      </c>
+      <c r="F131" t="s">
+        <v>39</v>
+      </c>
+      <c r="H131">
         <v>0.8099131779720991</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132">
+        <v>-6.431798275933005</v>
+      </c>
+      <c r="C132">
+        <v>3</v>
+      </c>
+      <c r="D132" t="s">
+        <v>44</v>
+      </c>
+      <c r="E132" t="s">
+        <v>43</v>
+      </c>
+      <c r="F132" t="s">
+        <v>39</v>
+      </c>
+      <c r="H132">
+        <v>0.301062406402033</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133">
+        <v>-6.431798275933005</v>
+      </c>
+      <c r="C133">
+        <v>4</v>
+      </c>
+      <c r="D133" t="s">
+        <v>44</v>
+      </c>
+      <c r="E133" t="s">
+        <v>43</v>
+      </c>
+      <c r="F133" t="s">
+        <v>39</v>
+      </c>
+      <c r="H133">
+        <v>0.149354087146788</v>
       </c>
     </row>
   </sheetData>
